--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,5284 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131344684</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>552919</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6469667</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131344703</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>552843</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6469679</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131344676</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>552946</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6469707</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131344688</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>552928</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6469662</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131344692</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79864</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>552907</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6469684</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131344654</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>552967</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6469782</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131344678</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>552948</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6469706</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131344679</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>552958</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6469695</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131344696</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>552909</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6469685</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131344647</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>552884</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6469766</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131344649</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>552893</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6469762</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131344707</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101220</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>552818</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6469626</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131344689</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>552921</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6469663</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131344698</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79864</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>552887</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6469694</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131344668</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>552947</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6469715</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131344686</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79864</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>552925</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6469645</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131344652</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>552916</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6469751</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131344682</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>552956</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6469666</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131344651</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>552908</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6469775</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131344677</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106138</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>552948</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6469713</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131344687</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>552921</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6469661</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131344683</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>552914</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6469649</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131344648</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>552878</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6469766</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131344658</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>553131</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6469899</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131344650</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>552899</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6469774</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131344663</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>553051</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6469833</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131344660</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>553080</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6469846</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131344670</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>552953</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6469707</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131344653</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>552954</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6469756</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131344646</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>552813</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6469703</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131344666</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>553049</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6469673</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131344674</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>552930</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6469714</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131344704</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>552824</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6469659</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131344680</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101220</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>552953</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6469664</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131344691</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>552922</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6469670</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131344659</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97883</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>553082</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6469843</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131344661</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>553051</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6469846</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131344705</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>552781</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6469669</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131344662</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>553053</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6469836</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131344645</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>552818</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6469702</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131344656</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>552998</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6469785</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131344685</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>552922</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6469668</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131344706</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>552813</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6469628</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131344669</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>552952</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6469713</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131344673</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58041</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>552942</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6469709</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>131344675</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>552941</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6469708</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131344657</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101220</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>552998</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6469788</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>131344667</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99018</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>552956</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6469709</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>131344655</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Södra Ändlöten, Ög</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>552976</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6469767</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Emil Ideskär</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Emil Ideskär, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -792,42 +792,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131344684</v>
+        <v>131344692</v>
       </c>
       <c r="B3" t="n">
-        <v>99018</v>
+        <v>79865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552919</v>
+        <v>552907</v>
       </c>
       <c r="R3" t="n">
-        <v>6469667</v>
+        <v>6469684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +900,7 @@
         <v>131344703</v>
       </c>
       <c r="B4" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1006,7 @@
         <v>131344676</v>
       </c>
       <c r="B5" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1112,7 @@
         <v>131344688</v>
       </c>
       <c r="B6" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,41 +1215,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131344692</v>
+        <v>131344684</v>
       </c>
       <c r="B7" t="n">
-        <v>79864</v>
+        <v>99019</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552907</v>
+        <v>552919</v>
       </c>
       <c r="R7" t="n">
-        <v>6469684</v>
+        <v>6469667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131344678</v>
+        <v>131344679</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552948</v>
+        <v>552958</v>
       </c>
       <c r="R9" t="n">
-        <v>6469706</v>
+        <v>6469695</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131344679</v>
+        <v>131344678</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552958</v>
+        <v>552948</v>
       </c>
       <c r="R10" t="n">
-        <v>6469695</v>
+        <v>6469706</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1767,37 +1767,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131344647</v>
+        <v>131344707</v>
       </c>
       <c r="B12" t="n">
-        <v>99018</v>
+        <v>101221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552884</v>
+        <v>552818</v>
       </c>
       <c r="R12" t="n">
-        <v>6469766</v>
+        <v>6469626</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,42 +1873,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344649</v>
+        <v>131344698</v>
       </c>
       <c r="B13" t="n">
-        <v>99018</v>
+        <v>79865</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1916,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552893</v>
+        <v>552887</v>
       </c>
       <c r="R13" t="n">
-        <v>6469762</v>
+        <v>6469694</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,37 +1978,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344707</v>
+        <v>131344689</v>
       </c>
       <c r="B14" t="n">
-        <v>101220</v>
+        <v>99019</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2022,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552818</v>
+        <v>552921</v>
       </c>
       <c r="R14" t="n">
-        <v>6469626</v>
+        <v>6469663</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344689</v>
+        <v>131344647</v>
       </c>
       <c r="B15" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2114,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2128,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552921</v>
+        <v>552884</v>
       </c>
       <c r="R15" t="n">
-        <v>6469663</v>
+        <v>6469766</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,41 +2190,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344698</v>
+        <v>131344649</v>
       </c>
       <c r="B16" t="n">
-        <v>79864</v>
+        <v>99019</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552887</v>
+        <v>552893</v>
       </c>
       <c r="R16" t="n">
-        <v>6469694</v>
+        <v>6469762</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,37 +2296,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131344668</v>
+        <v>131344677</v>
       </c>
       <c r="B17" t="n">
-        <v>99018</v>
+        <v>106140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552947</v>
+        <v>552948</v>
       </c>
       <c r="R17" t="n">
-        <v>6469715</v>
+        <v>6469713</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,41 +2402,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344686</v>
+        <v>131344651</v>
       </c>
       <c r="B18" t="n">
-        <v>79864</v>
+        <v>99019</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2444,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552925</v>
+        <v>552908</v>
       </c>
       <c r="R18" t="n">
-        <v>6469645</v>
+        <v>6469775</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2507,45 +2508,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344652</v>
+        <v>131344668</v>
       </c>
       <c r="B19" t="n">
-        <v>91834</v>
+        <v>99019</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2553,10 +2551,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552916</v>
+        <v>552947</v>
       </c>
       <c r="R19" t="n">
-        <v>6469751</v>
+        <v>6469715</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2730,42 +2728,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344651</v>
+        <v>131344686</v>
       </c>
       <c r="B21" t="n">
-        <v>99018</v>
+        <v>79865</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2773,10 +2770,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552908</v>
+        <v>552925</v>
       </c>
       <c r="R21" t="n">
-        <v>6469775</v>
+        <v>6469645</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,42 +2833,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131344677</v>
+        <v>131344652</v>
       </c>
       <c r="B22" t="n">
-        <v>106138</v>
+        <v>91835</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552948</v>
+        <v>552916</v>
       </c>
       <c r="R22" t="n">
-        <v>6469713</v>
+        <v>6469751</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131344687</v>
+        <v>131344683</v>
       </c>
       <c r="B23" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552921</v>
+        <v>552914</v>
       </c>
       <c r="R23" t="n">
-        <v>6469661</v>
+        <v>6469649</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131344683</v>
+        <v>131344687</v>
       </c>
       <c r="B24" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552914</v>
+        <v>552921</v>
       </c>
       <c r="R24" t="n">
-        <v>6469649</v>
+        <v>6469661</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3157,7 +3157,7 @@
         <v>131344648</v>
       </c>
       <c r="B25" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,46 +3260,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131344658</v>
+        <v>131344650</v>
       </c>
       <c r="B26" t="n">
-        <v>57881</v>
+        <v>99019</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3307,10 +3303,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>553131</v>
+        <v>552899</v>
       </c>
       <c r="R26" t="n">
-        <v>6469899</v>
+        <v>6469774</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3345,17 +3341,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3374,42 +3366,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131344650</v>
+        <v>131344658</v>
       </c>
       <c r="B27" t="n">
-        <v>99018</v>
+        <v>57881</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3417,10 +3413,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>552899</v>
+        <v>553131</v>
       </c>
       <c r="R27" t="n">
-        <v>6469774</v>
+        <v>6469899</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3455,13 +3451,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3483,7 +3483,7 @@
         <v>131344663</v>
       </c>
       <c r="B28" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131344660</v>
+        <v>131344670</v>
       </c>
       <c r="B29" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>553080</v>
+        <v>552953</v>
       </c>
       <c r="R29" t="n">
-        <v>6469846</v>
+        <v>6469707</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3695,10 +3695,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131344670</v>
+        <v>131344660</v>
       </c>
       <c r="B30" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>552953</v>
+        <v>553080</v>
       </c>
       <c r="R30" t="n">
-        <v>6469707</v>
+        <v>6469846</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3915,42 +3915,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131344646</v>
+        <v>131344674</v>
       </c>
       <c r="B32" t="n">
-        <v>99018</v>
+        <v>57881</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3958,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552813</v>
+        <v>552930</v>
       </c>
       <c r="R32" t="n">
-        <v>6469703</v>
+        <v>6469714</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,13 +4000,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4131,46 +4139,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131344674</v>
+        <v>131344704</v>
       </c>
       <c r="B34" t="n">
-        <v>57881</v>
+        <v>99019</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4178,10 +4182,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552930</v>
+        <v>552824</v>
       </c>
       <c r="R34" t="n">
-        <v>6469714</v>
+        <v>6469659</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4216,17 +4220,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131344704</v>
+        <v>131344646</v>
       </c>
       <c r="B35" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552824</v>
+        <v>552813</v>
       </c>
       <c r="R35" t="n">
-        <v>6469659</v>
+        <v>6469703</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4354,7 +4354,7 @@
         <v>131344680</v>
       </c>
       <c r="B36" t="n">
-        <v>101220</v>
+        <v>101221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>131344691</v>
       </c>
       <c r="B37" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4563,49 +4563,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131344659</v>
+        <v>131344661</v>
       </c>
       <c r="B38" t="n">
-        <v>97883</v>
+        <v>91835</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>553082</v>
+        <v>553051</v>
       </c>
       <c r="R38" t="n">
-        <v>6469843</v>
+        <v>6469846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4646,6 +4653,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4664,56 +4672,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131344661</v>
+        <v>131344659</v>
       </c>
       <c r="B39" t="n">
-        <v>91834</v>
+        <v>97884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>553051</v>
+        <v>553082</v>
       </c>
       <c r="R39" t="n">
-        <v>6469846</v>
+        <v>6469843</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4754,7 +4755,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4890,7 +4890,7 @@
         <v>131344662</v>
       </c>
       <c r="B41" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>131344645</v>
       </c>
       <c r="B42" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>131344656</v>
       </c>
       <c r="B43" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5208,10 +5208,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131344685</v>
+        <v>131344669</v>
       </c>
       <c r="B44" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552922</v>
+        <v>552952</v>
       </c>
       <c r="R44" t="n">
-        <v>6469668</v>
+        <v>6469713</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5314,46 +5314,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131344706</v>
+        <v>131344685</v>
       </c>
       <c r="B45" t="n">
-        <v>57881</v>
+        <v>99019</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5361,10 +5357,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552813</v>
+        <v>552922</v>
       </c>
       <c r="R45" t="n">
-        <v>6469628</v>
+        <v>6469668</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5399,17 +5395,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5428,10 +5420,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131344669</v>
+        <v>131344675</v>
       </c>
       <c r="B46" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,7 +5450,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5471,10 +5463,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552952</v>
+        <v>552941</v>
       </c>
       <c r="R46" t="n">
-        <v>6469713</v>
+        <v>6469708</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5534,46 +5526,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131344673</v>
+        <v>131344667</v>
       </c>
       <c r="B47" t="n">
-        <v>58041</v>
+        <v>99019</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5581,7 +5569,7 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552942</v>
+        <v>552956</v>
       </c>
       <c r="R47" t="n">
         <v>6469709</v>
@@ -5625,6 +5613,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5643,42 +5632,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131344675</v>
+        <v>131344706</v>
       </c>
       <c r="B48" t="n">
-        <v>99018</v>
+        <v>57881</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5686,10 +5679,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552941</v>
+        <v>552813</v>
       </c>
       <c r="R48" t="n">
-        <v>6469708</v>
+        <v>6469628</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5724,13 +5717,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5749,42 +5746,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131344657</v>
+        <v>131344673</v>
       </c>
       <c r="B49" t="n">
-        <v>101220</v>
+        <v>58041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>103020</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5792,10 +5793,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552998</v>
+        <v>552942</v>
       </c>
       <c r="R49" t="n">
-        <v>6469788</v>
+        <v>6469709</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5836,7 +5837,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5855,37 +5855,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344667</v>
+        <v>131344657</v>
       </c>
       <c r="B50" t="n">
-        <v>99018</v>
+        <v>101221</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -5898,10 +5898,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552956</v>
+        <v>552998</v>
       </c>
       <c r="R50" t="n">
-        <v>6469709</v>
+        <v>6469788</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5964,7 +5964,7 @@
         <v>131344655</v>
       </c>
       <c r="B51" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -1873,41 +1873,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344698</v>
+        <v>131344689</v>
       </c>
       <c r="B13" t="n">
-        <v>79865</v>
+        <v>99019</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1915,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552887</v>
+        <v>552921</v>
       </c>
       <c r="R13" t="n">
-        <v>6469694</v>
+        <v>6469663</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,7 +1979,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344689</v>
+        <v>131344647</v>
       </c>
       <c r="B14" t="n">
         <v>99019</v>
@@ -2008,7 +2009,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2021,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552921</v>
+        <v>552884</v>
       </c>
       <c r="R14" t="n">
-        <v>6469663</v>
+        <v>6469766</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,7 +2085,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344647</v>
+        <v>131344649</v>
       </c>
       <c r="B15" t="n">
         <v>99019</v>
@@ -2114,7 +2115,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2127,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552884</v>
+        <v>552893</v>
       </c>
       <c r="R15" t="n">
-        <v>6469766</v>
+        <v>6469762</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,42 +2191,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344649</v>
+        <v>131344698</v>
       </c>
       <c r="B16" t="n">
-        <v>99019</v>
+        <v>79865</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552893</v>
+        <v>552887</v>
       </c>
       <c r="R16" t="n">
-        <v>6469762</v>
+        <v>6469694</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -5208,37 +5208,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131344669</v>
+        <v>131344657</v>
       </c>
       <c r="B44" t="n">
-        <v>99019</v>
+        <v>101221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552952</v>
+        <v>552998</v>
       </c>
       <c r="R44" t="n">
-        <v>6469713</v>
+        <v>6469788</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131344685</v>
+        <v>131344669</v>
       </c>
       <c r="B45" t="n">
         <v>99019</v>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552922</v>
+        <v>552952</v>
       </c>
       <c r="R45" t="n">
-        <v>6469668</v>
+        <v>6469713</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5420,7 +5420,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131344675</v>
+        <v>131344685</v>
       </c>
       <c r="B46" t="n">
         <v>99019</v>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552941</v>
+        <v>552922</v>
       </c>
       <c r="R46" t="n">
-        <v>6469708</v>
+        <v>6469668</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131344667</v>
+        <v>131344675</v>
       </c>
       <c r="B47" t="n">
         <v>99019</v>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552956</v>
+        <v>552941</v>
       </c>
       <c r="R47" t="n">
-        <v>6469709</v>
+        <v>6469708</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5632,46 +5632,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131344706</v>
+        <v>131344667</v>
       </c>
       <c r="B48" t="n">
-        <v>57881</v>
+        <v>99019</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5679,10 +5675,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552813</v>
+        <v>552956</v>
       </c>
       <c r="R48" t="n">
-        <v>6469628</v>
+        <v>6469709</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5717,17 +5713,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5746,10 +5738,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131344673</v>
+        <v>131344706</v>
       </c>
       <c r="B49" t="n">
-        <v>58041</v>
+        <v>57881</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5757,16 +5749,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5793,10 +5785,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552942</v>
+        <v>552813</v>
       </c>
       <c r="R49" t="n">
-        <v>6469709</v>
+        <v>6469628</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5829,6 +5821,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5855,42 +5852,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344657</v>
+        <v>131344673</v>
       </c>
       <c r="B50" t="n">
-        <v>101221</v>
+        <v>58041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>103020</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5898,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552998</v>
+        <v>552942</v>
       </c>
       <c r="R50" t="n">
-        <v>6469788</v>
+        <v>6469709</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5942,7 +5943,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131344692</v>
       </c>
       <c r="B3" t="n">
-        <v>79865</v>
+        <v>79867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>131344703</v>
       </c>
       <c r="B4" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>131344676</v>
       </c>
       <c r="B5" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>131344688</v>
       </c>
       <c r="B6" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>131344684</v>
       </c>
       <c r="B7" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131344654</v>
+        <v>131344679</v>
       </c>
       <c r="B8" t="n">
-        <v>57881</v>
+        <v>91837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1354,13 +1354,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552967</v>
+        <v>552958</v>
       </c>
       <c r="R8" t="n">
-        <v>6469782</v>
+        <v>6469695</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,17 +1405,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1435,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131344679</v>
+        <v>131344678</v>
       </c>
       <c r="B9" t="n">
-        <v>91835</v>
+        <v>91837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,7 +1460,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1481,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552958</v>
+        <v>552948</v>
       </c>
       <c r="R9" t="n">
-        <v>6469695</v>
+        <v>6469706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131344678</v>
+        <v>131344654</v>
       </c>
       <c r="B10" t="n">
-        <v>91835</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,34 +1550,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1590,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552948</v>
+        <v>552967</v>
       </c>
       <c r="R10" t="n">
-        <v>6469706</v>
+        <v>6469782</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,13 +1624,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>131344696</v>
       </c>
       <c r="B11" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,42 +1767,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131344707</v>
+        <v>131344698</v>
       </c>
       <c r="B12" t="n">
-        <v>101221</v>
+        <v>79867</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1810,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552818</v>
+        <v>552887</v>
       </c>
       <c r="R12" t="n">
-        <v>6469626</v>
+        <v>6469694</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,37 +1872,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344689</v>
+        <v>131344707</v>
       </c>
       <c r="B13" t="n">
-        <v>99019</v>
+        <v>101223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1916,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552921</v>
+        <v>552818</v>
       </c>
       <c r="R13" t="n">
-        <v>6469663</v>
+        <v>6469626</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344647</v>
+        <v>131344689</v>
       </c>
       <c r="B14" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2008,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2022,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552884</v>
+        <v>552921</v>
       </c>
       <c r="R14" t="n">
-        <v>6469766</v>
+        <v>6469663</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344649</v>
+        <v>131344647</v>
       </c>
       <c r="B15" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2114,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2128,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552893</v>
+        <v>552884</v>
       </c>
       <c r="R15" t="n">
-        <v>6469762</v>
+        <v>6469766</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,41 +2190,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344698</v>
+        <v>131344649</v>
       </c>
       <c r="B16" t="n">
-        <v>79865</v>
+        <v>99021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552887</v>
+        <v>552893</v>
       </c>
       <c r="R16" t="n">
-        <v>6469694</v>
+        <v>6469762</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,42 +2296,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131344677</v>
+        <v>131344682</v>
       </c>
       <c r="B17" t="n">
-        <v>106140</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2339,10 +2343,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552948</v>
+        <v>552956</v>
       </c>
       <c r="R17" t="n">
-        <v>6469713</v>
+        <v>6469666</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,13 +2381,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2402,42 +2410,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344651</v>
+        <v>131344686</v>
       </c>
       <c r="B18" t="n">
-        <v>99019</v>
+        <v>79867</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2445,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552908</v>
+        <v>552925</v>
       </c>
       <c r="R18" t="n">
-        <v>6469775</v>
+        <v>6469645</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,42 +2515,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344668</v>
+        <v>131344652</v>
       </c>
       <c r="B19" t="n">
-        <v>99019</v>
+        <v>91837</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2551,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552947</v>
+        <v>552916</v>
       </c>
       <c r="R19" t="n">
-        <v>6469715</v>
+        <v>6469751</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,46 +2624,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344682</v>
+        <v>131344651</v>
       </c>
       <c r="B20" t="n">
-        <v>57881</v>
+        <v>99021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2661,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552956</v>
+        <v>552908</v>
       </c>
       <c r="R20" t="n">
-        <v>6469666</v>
+        <v>6469775</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,17 +2705,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2728,41 +2730,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344686</v>
+        <v>131344677</v>
       </c>
       <c r="B21" t="n">
-        <v>79865</v>
+        <v>106142</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2770,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552925</v>
+        <v>552948</v>
       </c>
       <c r="R21" t="n">
-        <v>6469645</v>
+        <v>6469713</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2833,45 +2836,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131344652</v>
+        <v>131344668</v>
       </c>
       <c r="B22" t="n">
-        <v>91835</v>
+        <v>99021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552916</v>
+        <v>552947</v>
       </c>
       <c r="R22" t="n">
-        <v>6469751</v>
+        <v>6469715</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2945,7 +2945,7 @@
         <v>131344683</v>
       </c>
       <c r="B23" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>131344687</v>
       </c>
       <c r="B24" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>131344648</v>
       </c>
       <c r="B25" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,42 +3260,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131344650</v>
+        <v>131344663</v>
       </c>
       <c r="B26" t="n">
-        <v>99019</v>
+        <v>91837</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3303,10 +3306,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552899</v>
+        <v>553051</v>
       </c>
       <c r="R26" t="n">
-        <v>6469774</v>
+        <v>6469833</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3369,7 +3372,7 @@
         <v>131344658</v>
       </c>
       <c r="B27" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,45 +3483,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131344663</v>
+        <v>131344650</v>
       </c>
       <c r="B28" t="n">
-        <v>91835</v>
+        <v>99021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>553051</v>
+        <v>552899</v>
       </c>
       <c r="R28" t="n">
-        <v>6469833</v>
+        <v>6469774</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3592,7 +3592,7 @@
         <v>131344670</v>
       </c>
       <c r="B29" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>131344660</v>
       </c>
       <c r="B30" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>131344653</v>
       </c>
       <c r="B31" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>131344674</v>
       </c>
       <c r="B32" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>131344666</v>
       </c>
       <c r="B33" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>131344704</v>
       </c>
       <c r="B34" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>131344646</v>
       </c>
       <c r="B35" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>131344680</v>
       </c>
       <c r="B36" t="n">
-        <v>101221</v>
+        <v>101223</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>131344691</v>
       </c>
       <c r="B37" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>131344661</v>
       </c>
       <c r="B38" t="n">
-        <v>91835</v>
+        <v>91837</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>131344659</v>
       </c>
       <c r="B39" t="n">
-        <v>97884</v>
+        <v>97886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>131344705</v>
       </c>
       <c r="B40" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>131344662</v>
       </c>
       <c r="B41" t="n">
-        <v>91835</v>
+        <v>91837</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>131344645</v>
       </c>
       <c r="B42" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>131344656</v>
       </c>
       <c r="B43" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5208,42 +5208,46 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131344657</v>
+        <v>131344673</v>
       </c>
       <c r="B44" t="n">
-        <v>101221</v>
+        <v>58043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>103020</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5251,10 +5255,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552998</v>
+        <v>552942</v>
       </c>
       <c r="R44" t="n">
-        <v>6469788</v>
+        <v>6469709</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5295,7 +5299,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5317,7 +5320,7 @@
         <v>131344669</v>
       </c>
       <c r="B45" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5423,7 +5426,7 @@
         <v>131344685</v>
       </c>
       <c r="B46" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5529,7 +5532,7 @@
         <v>131344675</v>
       </c>
       <c r="B47" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5635,7 +5638,7 @@
         <v>131344667</v>
       </c>
       <c r="B48" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5741,7 +5744,7 @@
         <v>131344706</v>
       </c>
       <c r="B49" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5852,46 +5855,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344673</v>
+        <v>131344657</v>
       </c>
       <c r="B50" t="n">
-        <v>58041</v>
+        <v>101223</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103020</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5899,10 +5898,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552942</v>
+        <v>552998</v>
       </c>
       <c r="R50" t="n">
-        <v>6469709</v>
+        <v>6469788</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5943,6 +5942,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5964,7 +5964,7 @@
         <v>131344655</v>
       </c>
       <c r="B51" t="n">
-        <v>91835</v>
+        <v>91837</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131344692</v>
       </c>
       <c r="B3" t="n">
-        <v>79867</v>
+        <v>79868</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>131344703</v>
       </c>
       <c r="B4" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>131344676</v>
       </c>
       <c r="B5" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>131344688</v>
       </c>
       <c r="B6" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>131344684</v>
       </c>
       <c r="B7" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131344679</v>
+        <v>131344654</v>
       </c>
       <c r="B8" t="n">
-        <v>91837</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1354,12 +1354,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552958</v>
+        <v>552967</v>
       </c>
       <c r="R8" t="n">
-        <v>6469695</v>
+        <v>6469782</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,13 +1406,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1430,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131344678</v>
+        <v>131344679</v>
       </c>
       <c r="B9" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,7 +1465,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1476,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552948</v>
+        <v>552958</v>
       </c>
       <c r="R9" t="n">
-        <v>6469706</v>
+        <v>6469695</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131344654</v>
+        <v>131344678</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>91838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,35 +1555,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1586,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552967</v>
+        <v>552948</v>
       </c>
       <c r="R10" t="n">
-        <v>6469782</v>
+        <v>6469706</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,17 +1628,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>131344696</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>131344698</v>
       </c>
       <c r="B12" t="n">
-        <v>79867</v>
+        <v>79868</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,37 +1872,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344707</v>
+        <v>131344689</v>
       </c>
       <c r="B13" t="n">
-        <v>101223</v>
+        <v>99022</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552818</v>
+        <v>552921</v>
       </c>
       <c r="R13" t="n">
-        <v>6469626</v>
+        <v>6469663</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344689</v>
+        <v>131344647</v>
       </c>
       <c r="B14" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552921</v>
+        <v>552884</v>
       </c>
       <c r="R14" t="n">
-        <v>6469663</v>
+        <v>6469766</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344647</v>
+        <v>131344649</v>
       </c>
       <c r="B15" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552884</v>
+        <v>552893</v>
       </c>
       <c r="R15" t="n">
-        <v>6469766</v>
+        <v>6469762</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,37 +2190,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344649</v>
+        <v>131344707</v>
       </c>
       <c r="B16" t="n">
-        <v>99021</v>
+        <v>101224</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552893</v>
+        <v>552818</v>
       </c>
       <c r="R16" t="n">
-        <v>6469762</v>
+        <v>6469626</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2299,7 +2299,7 @@
         <v>131344682</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>131344686</v>
       </c>
       <c r="B18" t="n">
-        <v>79867</v>
+        <v>79868</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>131344652</v>
       </c>
       <c r="B19" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>131344651</v>
       </c>
       <c r="B20" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>131344677</v>
       </c>
       <c r="B21" t="n">
-        <v>106142</v>
+        <v>106143</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>131344668</v>
       </c>
       <c r="B22" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>131344683</v>
       </c>
       <c r="B23" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>131344687</v>
       </c>
       <c r="B24" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>131344648</v>
       </c>
       <c r="B25" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131344663</v>
+        <v>131344658</v>
       </c>
       <c r="B26" t="n">
-        <v>91837</v>
+        <v>57884</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3293,12 +3293,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3306,10 +3307,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>553051</v>
+        <v>553131</v>
       </c>
       <c r="R26" t="n">
-        <v>6469833</v>
+        <v>6469899</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,13 +3345,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3369,10 +3374,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131344658</v>
+        <v>131344663</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>91838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3380,21 +3385,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3402,13 +3407,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3416,10 +3420,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>553131</v>
+        <v>553051</v>
       </c>
       <c r="R27" t="n">
-        <v>6469899</v>
+        <v>6469833</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3454,17 +3458,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>131344650</v>
       </c>
       <c r="B28" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>131344670</v>
       </c>
       <c r="B29" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>131344660</v>
       </c>
       <c r="B30" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>131344653</v>
       </c>
       <c r="B31" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3915,46 +3915,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131344674</v>
+        <v>131344704</v>
       </c>
       <c r="B32" t="n">
-        <v>57883</v>
+        <v>99022</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3962,10 +3958,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552930</v>
+        <v>552824</v>
       </c>
       <c r="R32" t="n">
-        <v>6469714</v>
+        <v>6469659</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4000,17 +3996,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4029,42 +4021,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131344666</v>
+        <v>131344646</v>
       </c>
       <c r="B33" t="n">
-        <v>57883</v>
+        <v>99022</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4072,10 +4064,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>553049</v>
+        <v>552813</v>
       </c>
       <c r="R33" t="n">
-        <v>6469673</v>
+        <v>6469703</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4110,17 +4102,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4139,42 +4127,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131344704</v>
+        <v>131344674</v>
       </c>
       <c r="B34" t="n">
-        <v>99021</v>
+        <v>57884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4182,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552824</v>
+        <v>552930</v>
       </c>
       <c r="R34" t="n">
-        <v>6469659</v>
+        <v>6469714</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4220,13 +4212,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4245,42 +4241,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131344646</v>
+        <v>131344666</v>
       </c>
       <c r="B35" t="n">
-        <v>99021</v>
+        <v>57884</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4288,10 +4284,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552813</v>
+        <v>553049</v>
       </c>
       <c r="R35" t="n">
-        <v>6469703</v>
+        <v>6469673</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4326,13 +4322,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>131344680</v>
       </c>
       <c r="B36" t="n">
-        <v>101223</v>
+        <v>101224</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>131344691</v>
       </c>
       <c r="B37" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4563,56 +4563,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131344661</v>
+        <v>131344659</v>
       </c>
       <c r="B38" t="n">
-        <v>91837</v>
+        <v>97887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>553051</v>
+        <v>553082</v>
       </c>
       <c r="R38" t="n">
-        <v>6469846</v>
+        <v>6469843</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4653,7 +4646,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4672,49 +4664,56 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131344659</v>
+        <v>131344661</v>
       </c>
       <c r="B39" t="n">
-        <v>97886</v>
+        <v>91838</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>553082</v>
+        <v>553051</v>
       </c>
       <c r="R39" t="n">
-        <v>6469843</v>
+        <v>6469846</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4755,6 +4754,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4773,46 +4773,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131344705</v>
+        <v>131344645</v>
       </c>
       <c r="B40" t="n">
-        <v>57883</v>
+        <v>99022</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4820,10 +4816,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552781</v>
+        <v>552818</v>
       </c>
       <c r="R40" t="n">
-        <v>6469669</v>
+        <v>6469702</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4858,17 +4854,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4887,10 +4879,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131344662</v>
+        <v>131344705</v>
       </c>
       <c r="B41" t="n">
-        <v>91837</v>
+        <v>57884</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4898,21 +4890,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4920,12 +4912,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4933,10 +4926,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>553053</v>
+        <v>552781</v>
       </c>
       <c r="R41" t="n">
-        <v>6469836</v>
+        <v>6469669</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4971,13 +4964,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4996,42 +4993,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131344645</v>
+        <v>131344662</v>
       </c>
       <c r="B42" t="n">
-        <v>99021</v>
+        <v>91838</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>552818</v>
+        <v>553053</v>
       </c>
       <c r="R42" t="n">
-        <v>6469702</v>
+        <v>6469836</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5105,7 +5105,7 @@
         <v>131344656</v>
       </c>
       <c r="B43" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5208,46 +5208,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131344673</v>
+        <v>131344657</v>
       </c>
       <c r="B44" t="n">
-        <v>58043</v>
+        <v>101224</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103020</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5255,10 +5251,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552942</v>
+        <v>552998</v>
       </c>
       <c r="R44" t="n">
-        <v>6469709</v>
+        <v>6469788</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5299,6 +5295,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5317,42 +5314,46 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131344669</v>
+        <v>131344706</v>
       </c>
       <c r="B45" t="n">
-        <v>99021</v>
+        <v>57884</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5360,10 +5361,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552952</v>
+        <v>552813</v>
       </c>
       <c r="R45" t="n">
-        <v>6469713</v>
+        <v>6469628</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5398,13 +5399,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5423,42 +5428,46 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131344685</v>
+        <v>131344673</v>
       </c>
       <c r="B46" t="n">
-        <v>99021</v>
+        <v>58044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5466,10 +5475,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552922</v>
+        <v>552942</v>
       </c>
       <c r="R46" t="n">
-        <v>6469668</v>
+        <v>6469709</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5510,7 +5519,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5529,10 +5537,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131344675</v>
+        <v>131344669</v>
       </c>
       <c r="B47" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5559,7 +5567,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5572,10 +5580,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552941</v>
+        <v>552952</v>
       </c>
       <c r="R47" t="n">
-        <v>6469708</v>
+        <v>6469713</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5635,10 +5643,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131344667</v>
+        <v>131344685</v>
       </c>
       <c r="B48" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5665,7 +5673,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -5678,10 +5686,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552956</v>
+        <v>552922</v>
       </c>
       <c r="R48" t="n">
-        <v>6469709</v>
+        <v>6469668</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5741,46 +5749,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131344706</v>
+        <v>131344675</v>
       </c>
       <c r="B49" t="n">
-        <v>57883</v>
+        <v>99022</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5788,10 +5792,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552813</v>
+        <v>552941</v>
       </c>
       <c r="R49" t="n">
-        <v>6469628</v>
+        <v>6469708</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5826,17 +5830,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5855,37 +5855,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344657</v>
+        <v>131344667</v>
       </c>
       <c r="B50" t="n">
-        <v>101223</v>
+        <v>99022</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -5898,10 +5898,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552998</v>
+        <v>552956</v>
       </c>
       <c r="R50" t="n">
-        <v>6469788</v>
+        <v>6469709</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5964,7 +5964,7 @@
         <v>131344655</v>
       </c>
       <c r="B51" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -1767,41 +1767,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131344698</v>
+        <v>131344707</v>
       </c>
       <c r="B12" t="n">
-        <v>79868</v>
+        <v>101224</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1809,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552887</v>
+        <v>552818</v>
       </c>
       <c r="R12" t="n">
-        <v>6469694</v>
+        <v>6469626</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2190,42 +2191,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344707</v>
+        <v>131344698</v>
       </c>
       <c r="B16" t="n">
-        <v>101224</v>
+        <v>79868</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552818</v>
+        <v>552887</v>
       </c>
       <c r="R16" t="n">
-        <v>6469626</v>
+        <v>6469694</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344686</v>
+        <v>131344652</v>
       </c>
       <c r="B18" t="n">
-        <v>79868</v>
+        <v>91838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,21 +2421,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2443,7 +2443,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2452,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552925</v>
+        <v>552916</v>
       </c>
       <c r="R18" t="n">
-        <v>6469645</v>
+        <v>6469751</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2515,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344652</v>
+        <v>131344686</v>
       </c>
       <c r="B19" t="n">
-        <v>91838</v>
+        <v>79868</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2526,21 +2530,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2548,11 +2552,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552916</v>
+        <v>552925</v>
       </c>
       <c r="R19" t="n">
-        <v>6469751</v>
+        <v>6469645</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2624,37 +2624,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344651</v>
+        <v>131344677</v>
       </c>
       <c r="B20" t="n">
-        <v>99022</v>
+        <v>106143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552908</v>
+        <v>552948</v>
       </c>
       <c r="R20" t="n">
-        <v>6469775</v>
+        <v>6469713</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,37 +2730,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344677</v>
+        <v>131344651</v>
       </c>
       <c r="B21" t="n">
-        <v>106143</v>
+        <v>99022</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552948</v>
+        <v>552908</v>
       </c>
       <c r="R21" t="n">
-        <v>6469713</v>
+        <v>6469775</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131344658</v>
+        <v>131344663</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>91838</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3293,13 +3293,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3307,10 +3306,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>553131</v>
+        <v>553051</v>
       </c>
       <c r="R26" t="n">
-        <v>6469899</v>
+        <v>6469833</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3345,17 +3344,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3374,45 +3369,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131344663</v>
+        <v>131344650</v>
       </c>
       <c r="B27" t="n">
-        <v>91838</v>
+        <v>99022</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3420,10 +3412,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>553051</v>
+        <v>552899</v>
       </c>
       <c r="R27" t="n">
-        <v>6469833</v>
+        <v>6469774</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3483,42 +3475,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131344650</v>
+        <v>131344658</v>
       </c>
       <c r="B28" t="n">
-        <v>99022</v>
+        <v>57884</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3526,10 +3522,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>552899</v>
+        <v>553131</v>
       </c>
       <c r="R28" t="n">
-        <v>6469774</v>
+        <v>6469899</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3564,13 +3560,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3915,42 +3915,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131344704</v>
+        <v>131344674</v>
       </c>
       <c r="B32" t="n">
-        <v>99022</v>
+        <v>57884</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3958,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552824</v>
+        <v>552930</v>
       </c>
       <c r="R32" t="n">
-        <v>6469659</v>
+        <v>6469714</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,13 +4000,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4021,7 +4029,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131344646</v>
+        <v>131344704</v>
       </c>
       <c r="B33" t="n">
         <v>99022</v>
@@ -4051,7 +4059,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4064,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552813</v>
+        <v>552824</v>
       </c>
       <c r="R33" t="n">
-        <v>6469703</v>
+        <v>6469659</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4127,46 +4135,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131344674</v>
+        <v>131344646</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>99022</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4174,10 +4178,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552930</v>
+        <v>552813</v>
       </c>
       <c r="R34" t="n">
-        <v>6469714</v>
+        <v>6469703</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4212,17 +4216,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4563,49 +4563,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131344659</v>
+        <v>131344661</v>
       </c>
       <c r="B38" t="n">
-        <v>97887</v>
+        <v>91838</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>553082</v>
+        <v>553051</v>
       </c>
       <c r="R38" t="n">
-        <v>6469843</v>
+        <v>6469846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4646,6 +4653,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4664,56 +4672,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131344661</v>
+        <v>131344659</v>
       </c>
       <c r="B39" t="n">
-        <v>91838</v>
+        <v>97887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>553051</v>
+        <v>553082</v>
       </c>
       <c r="R39" t="n">
-        <v>6469846</v>
+        <v>6469843</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4754,7 +4755,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4773,42 +4773,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131344645</v>
+        <v>131344662</v>
       </c>
       <c r="B40" t="n">
-        <v>99022</v>
+        <v>91838</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4816,10 +4819,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552818</v>
+        <v>553053</v>
       </c>
       <c r="R40" t="n">
-        <v>6469702</v>
+        <v>6469836</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4879,46 +4882,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131344705</v>
+        <v>131344645</v>
       </c>
       <c r="B41" t="n">
-        <v>57884</v>
+        <v>99022</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4926,10 +4925,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>552781</v>
+        <v>552818</v>
       </c>
       <c r="R41" t="n">
-        <v>6469669</v>
+        <v>6469702</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4964,17 +4963,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4993,10 +4988,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131344662</v>
+        <v>131344705</v>
       </c>
       <c r="B42" t="n">
-        <v>91838</v>
+        <v>57884</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5004,21 +4999,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5026,12 +5021,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5039,10 +5035,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>553053</v>
+        <v>552781</v>
       </c>
       <c r="R42" t="n">
-        <v>6469836</v>
+        <v>6469669</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5077,13 +5073,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5208,37 +5208,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131344657</v>
+        <v>131344669</v>
       </c>
       <c r="B44" t="n">
-        <v>101224</v>
+        <v>99022</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552998</v>
+        <v>552952</v>
       </c>
       <c r="R44" t="n">
-        <v>6469788</v>
+        <v>6469713</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5314,46 +5314,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131344706</v>
+        <v>131344685</v>
       </c>
       <c r="B45" t="n">
-        <v>57884</v>
+        <v>99022</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5361,10 +5357,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552813</v>
+        <v>552922</v>
       </c>
       <c r="R45" t="n">
-        <v>6469628</v>
+        <v>6469668</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5399,17 +5395,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5428,46 +5420,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131344673</v>
+        <v>131344675</v>
       </c>
       <c r="B46" t="n">
-        <v>58044</v>
+        <v>99022</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5475,10 +5463,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552942</v>
+        <v>552941</v>
       </c>
       <c r="R46" t="n">
-        <v>6469709</v>
+        <v>6469708</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5519,6 +5507,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5537,7 +5526,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131344669</v>
+        <v>131344667</v>
       </c>
       <c r="B47" t="n">
         <v>99022</v>
@@ -5567,7 +5556,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5580,10 +5569,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552952</v>
+        <v>552956</v>
       </c>
       <c r="R47" t="n">
-        <v>6469713</v>
+        <v>6469709</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5643,42 +5632,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131344685</v>
+        <v>131344706</v>
       </c>
       <c r="B48" t="n">
-        <v>99022</v>
+        <v>57884</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5686,10 +5679,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552922</v>
+        <v>552813</v>
       </c>
       <c r="R48" t="n">
-        <v>6469668</v>
+        <v>6469628</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5724,13 +5717,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5749,42 +5746,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131344675</v>
+        <v>131344673</v>
       </c>
       <c r="B49" t="n">
-        <v>99022</v>
+        <v>58044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5792,10 +5793,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552941</v>
+        <v>552942</v>
       </c>
       <c r="R49" t="n">
-        <v>6469708</v>
+        <v>6469709</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5836,7 +5837,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5855,37 +5855,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344667</v>
+        <v>131344657</v>
       </c>
       <c r="B50" t="n">
-        <v>99022</v>
+        <v>101224</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -5898,10 +5898,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552956</v>
+        <v>552998</v>
       </c>
       <c r="R50" t="n">
-        <v>6469709</v>
+        <v>6469788</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -792,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131344692</v>
+        <v>131344703</v>
       </c>
       <c r="B3" t="n">
-        <v>79868</v>
+        <v>99022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,6 +827,7 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552907</v>
+        <v>552843</v>
       </c>
       <c r="R3" t="n">
-        <v>6469684</v>
+        <v>6469679</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131344703</v>
+        <v>131344676</v>
       </c>
       <c r="B4" t="n">
         <v>99022</v>
@@ -927,7 +928,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -940,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552843</v>
+        <v>552946</v>
       </c>
       <c r="R4" t="n">
-        <v>6469679</v>
+        <v>6469707</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1004,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131344676</v>
+        <v>131344688</v>
       </c>
       <c r="B5" t="n">
         <v>99022</v>
@@ -1033,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1046,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552946</v>
+        <v>552928</v>
       </c>
       <c r="R5" t="n">
-        <v>6469707</v>
+        <v>6469662</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131344688</v>
+        <v>131344684</v>
       </c>
       <c r="B6" t="n">
         <v>99022</v>
@@ -1139,7 +1140,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1152,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552928</v>
+        <v>552919</v>
       </c>
       <c r="R6" t="n">
-        <v>6469662</v>
+        <v>6469667</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,42 +1216,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131344684</v>
+        <v>131344692</v>
       </c>
       <c r="B7" t="n">
-        <v>99022</v>
+        <v>79868</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552919</v>
+        <v>552907</v>
       </c>
       <c r="R7" t="n">
-        <v>6469667</v>
+        <v>6469684</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131344654</v>
+        <v>131344679</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>91838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1354,13 +1354,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552967</v>
+        <v>552958</v>
       </c>
       <c r="R8" t="n">
-        <v>6469782</v>
+        <v>6469695</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,17 +1405,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1435,7 +1430,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131344679</v>
+        <v>131344678</v>
       </c>
       <c r="B9" t="n">
         <v>91838</v>
@@ -1465,7 +1460,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1481,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552958</v>
+        <v>552948</v>
       </c>
       <c r="R9" t="n">
-        <v>6469695</v>
+        <v>6469706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131344678</v>
+        <v>131344654</v>
       </c>
       <c r="B10" t="n">
-        <v>91838</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,34 +1550,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1590,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552948</v>
+        <v>552967</v>
       </c>
       <c r="R10" t="n">
-        <v>6469706</v>
+        <v>6469782</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,13 +1624,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1767,42 +1767,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131344707</v>
+        <v>131344698</v>
       </c>
       <c r="B12" t="n">
-        <v>101224</v>
+        <v>79868</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1810,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552818</v>
+        <v>552887</v>
       </c>
       <c r="R12" t="n">
-        <v>6469626</v>
+        <v>6469694</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2191,41 +2190,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344698</v>
+        <v>131344707</v>
       </c>
       <c r="B16" t="n">
-        <v>79868</v>
+        <v>101224</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552887</v>
+        <v>552818</v>
       </c>
       <c r="R16" t="n">
-        <v>6469694</v>
+        <v>6469626</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,46 +2296,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131344682</v>
+        <v>131344651</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>99022</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2343,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552956</v>
+        <v>552908</v>
       </c>
       <c r="R17" t="n">
-        <v>6469666</v>
+        <v>6469775</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,17 +2377,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2410,45 +2402,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344652</v>
+        <v>131344677</v>
       </c>
       <c r="B18" t="n">
-        <v>91838</v>
+        <v>106143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2456,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552916</v>
+        <v>552948</v>
       </c>
       <c r="R18" t="n">
-        <v>6469751</v>
+        <v>6469713</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,41 +2508,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344686</v>
+        <v>131344668</v>
       </c>
       <c r="B19" t="n">
-        <v>79868</v>
+        <v>99022</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2561,10 +2551,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552925</v>
+        <v>552947</v>
       </c>
       <c r="R19" t="n">
-        <v>6469645</v>
+        <v>6469715</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2624,42 +2614,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344677</v>
+        <v>131344686</v>
       </c>
       <c r="B20" t="n">
-        <v>106143</v>
+        <v>79868</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2667,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552948</v>
+        <v>552925</v>
       </c>
       <c r="R20" t="n">
-        <v>6469713</v>
+        <v>6469645</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,42 +2719,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344651</v>
+        <v>131344652</v>
       </c>
       <c r="B21" t="n">
-        <v>99022</v>
+        <v>91838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2773,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552908</v>
+        <v>552916</v>
       </c>
       <c r="R21" t="n">
-        <v>6469775</v>
+        <v>6469751</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,42 +2828,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131344668</v>
+        <v>131344682</v>
       </c>
       <c r="B22" t="n">
-        <v>99022</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2879,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552947</v>
+        <v>552956</v>
       </c>
       <c r="R22" t="n">
-        <v>6469715</v>
+        <v>6469666</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2917,13 +2913,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3260,45 +3260,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131344663</v>
+        <v>131344650</v>
       </c>
       <c r="B26" t="n">
-        <v>91838</v>
+        <v>99022</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3306,10 +3303,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>553051</v>
+        <v>552899</v>
       </c>
       <c r="R26" t="n">
-        <v>6469833</v>
+        <v>6469774</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3369,42 +3366,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131344650</v>
+        <v>131344663</v>
       </c>
       <c r="B27" t="n">
-        <v>99022</v>
+        <v>91838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>552899</v>
+        <v>553051</v>
       </c>
       <c r="R27" t="n">
-        <v>6469774</v>
+        <v>6469833</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3915,46 +3915,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131344674</v>
+        <v>131344704</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>99022</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3962,10 +3958,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552930</v>
+        <v>552824</v>
       </c>
       <c r="R32" t="n">
-        <v>6469714</v>
+        <v>6469659</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4000,17 +3996,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4029,7 +4021,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131344704</v>
+        <v>131344646</v>
       </c>
       <c r="B33" t="n">
         <v>99022</v>
@@ -4059,7 +4051,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4072,10 +4064,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552824</v>
+        <v>552813</v>
       </c>
       <c r="R33" t="n">
-        <v>6469659</v>
+        <v>6469703</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4135,42 +4127,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131344646</v>
+        <v>131344674</v>
       </c>
       <c r="B34" t="n">
-        <v>99022</v>
+        <v>57884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4178,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552813</v>
+        <v>552930</v>
       </c>
       <c r="R34" t="n">
-        <v>6469703</v>
+        <v>6469714</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4216,13 +4212,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4882,42 +4882,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131344645</v>
+        <v>131344705</v>
       </c>
       <c r="B41" t="n">
-        <v>99022</v>
+        <v>57884</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4925,10 +4929,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>552818</v>
+        <v>552781</v>
       </c>
       <c r="R41" t="n">
-        <v>6469702</v>
+        <v>6469669</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4963,13 +4967,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4988,46 +4996,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131344705</v>
+        <v>131344645</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>99022</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5035,10 +5039,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>552781</v>
+        <v>552818</v>
       </c>
       <c r="R42" t="n">
-        <v>6469669</v>
+        <v>6469702</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,17 +5077,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5208,42 +5208,46 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131344669</v>
+        <v>131344706</v>
       </c>
       <c r="B44" t="n">
-        <v>99022</v>
+        <v>57884</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5251,10 +5255,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552952</v>
+        <v>552813</v>
       </c>
       <c r="R44" t="n">
-        <v>6469713</v>
+        <v>6469628</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5289,13 +5293,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5314,7 +5322,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131344685</v>
+        <v>131344669</v>
       </c>
       <c r="B45" t="n">
         <v>99022</v>
@@ -5344,7 +5352,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -5357,10 +5365,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552922</v>
+        <v>552952</v>
       </c>
       <c r="R45" t="n">
-        <v>6469668</v>
+        <v>6469713</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5420,7 +5428,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131344675</v>
+        <v>131344685</v>
       </c>
       <c r="B46" t="n">
         <v>99022</v>
@@ -5450,7 +5458,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5463,10 +5471,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552941</v>
+        <v>552922</v>
       </c>
       <c r="R46" t="n">
-        <v>6469708</v>
+        <v>6469668</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5526,7 +5534,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131344667</v>
+        <v>131344675</v>
       </c>
       <c r="B47" t="n">
         <v>99022</v>
@@ -5556,7 +5564,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5569,10 +5577,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552956</v>
+        <v>552941</v>
       </c>
       <c r="R47" t="n">
-        <v>6469709</v>
+        <v>6469708</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5632,46 +5640,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131344706</v>
+        <v>131344667</v>
       </c>
       <c r="B48" t="n">
-        <v>57884</v>
+        <v>99022</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5679,10 +5683,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552813</v>
+        <v>552956</v>
       </c>
       <c r="R48" t="n">
-        <v>6469628</v>
+        <v>6469709</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5717,17 +5721,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5746,46 +5746,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131344673</v>
+        <v>131344657</v>
       </c>
       <c r="B49" t="n">
-        <v>58044</v>
+        <v>101224</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103020</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5793,10 +5789,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552942</v>
+        <v>552998</v>
       </c>
       <c r="R49" t="n">
-        <v>6469709</v>
+        <v>6469788</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5837,6 +5833,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5855,42 +5852,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344657</v>
+        <v>131344673</v>
       </c>
       <c r="B50" t="n">
-        <v>101224</v>
+        <v>58044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>103020</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5898,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552998</v>
+        <v>552942</v>
       </c>
       <c r="R50" t="n">
-        <v>6469788</v>
+        <v>6469709</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5942,7 +5943,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -792,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131344703</v>
+        <v>131344692</v>
       </c>
       <c r="B3" t="n">
-        <v>99022</v>
+        <v>79869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,7 +827,6 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552843</v>
+        <v>552907</v>
       </c>
       <c r="R3" t="n">
-        <v>6469679</v>
+        <v>6469684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131344676</v>
+        <v>131344703</v>
       </c>
       <c r="B4" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -941,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552946</v>
+        <v>552843</v>
       </c>
       <c r="R4" t="n">
-        <v>6469707</v>
+        <v>6469679</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131344688</v>
+        <v>131344676</v>
       </c>
       <c r="B5" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,7 +1033,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1047,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552928</v>
+        <v>552946</v>
       </c>
       <c r="R5" t="n">
-        <v>6469662</v>
+        <v>6469707</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131344684</v>
+        <v>131344688</v>
       </c>
       <c r="B6" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,7 +1139,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1153,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552919</v>
+        <v>552928</v>
       </c>
       <c r="R6" t="n">
-        <v>6469667</v>
+        <v>6469662</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,41 +1215,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131344692</v>
+        <v>131344684</v>
       </c>
       <c r="B7" t="n">
-        <v>79868</v>
+        <v>99023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552907</v>
+        <v>552919</v>
       </c>
       <c r="R7" t="n">
-        <v>6469684</v>
+        <v>6469667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1324,7 @@
         <v>131344679</v>
       </c>
       <c r="B8" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>131344678</v>
       </c>
       <c r="B9" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>131344654</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>131344696</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>131344698</v>
       </c>
       <c r="B12" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,37 +1872,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344689</v>
+        <v>131344707</v>
       </c>
       <c r="B13" t="n">
-        <v>99022</v>
+        <v>101225</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552921</v>
+        <v>552818</v>
       </c>
       <c r="R13" t="n">
-        <v>6469663</v>
+        <v>6469626</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344647</v>
+        <v>131344689</v>
       </c>
       <c r="B14" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552884</v>
+        <v>552921</v>
       </c>
       <c r="R14" t="n">
-        <v>6469766</v>
+        <v>6469663</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344649</v>
+        <v>131344647</v>
       </c>
       <c r="B15" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552893</v>
+        <v>552884</v>
       </c>
       <c r="R15" t="n">
-        <v>6469762</v>
+        <v>6469766</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,37 +2190,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344707</v>
+        <v>131344649</v>
       </c>
       <c r="B16" t="n">
-        <v>101224</v>
+        <v>99023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552818</v>
+        <v>552893</v>
       </c>
       <c r="R16" t="n">
-        <v>6469626</v>
+        <v>6469762</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,42 +2296,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131344651</v>
+        <v>131344686</v>
       </c>
       <c r="B17" t="n">
-        <v>99022</v>
+        <v>79869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2339,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552908</v>
+        <v>552925</v>
       </c>
       <c r="R17" t="n">
-        <v>6469775</v>
+        <v>6469645</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,42 +2401,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344677</v>
+        <v>131344652</v>
       </c>
       <c r="B18" t="n">
-        <v>106143</v>
+        <v>91839</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2445,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552948</v>
+        <v>552916</v>
       </c>
       <c r="R18" t="n">
-        <v>6469713</v>
+        <v>6469751</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,42 +2510,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344668</v>
+        <v>131344682</v>
       </c>
       <c r="B19" t="n">
-        <v>99022</v>
+        <v>57885</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2551,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552947</v>
+        <v>552956</v>
       </c>
       <c r="R19" t="n">
-        <v>6469715</v>
+        <v>6469666</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,13 +2595,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2614,41 +2624,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344686</v>
+        <v>131344677</v>
       </c>
       <c r="B20" t="n">
-        <v>79868</v>
+        <v>106144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2656,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552925</v>
+        <v>552948</v>
       </c>
       <c r="R20" t="n">
-        <v>6469645</v>
+        <v>6469713</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2719,45 +2730,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344652</v>
+        <v>131344651</v>
       </c>
       <c r="B21" t="n">
-        <v>91838</v>
+        <v>99023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2765,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552916</v>
+        <v>552908</v>
       </c>
       <c r="R21" t="n">
-        <v>6469751</v>
+        <v>6469775</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,46 +2836,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131344682</v>
+        <v>131344668</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>99023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2875,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552956</v>
+        <v>552947</v>
       </c>
       <c r="R22" t="n">
-        <v>6469666</v>
+        <v>6469715</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,17 +2917,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>131344683</v>
       </c>
       <c r="B23" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>131344687</v>
       </c>
       <c r="B24" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>131344648</v>
       </c>
       <c r="B25" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,42 +3260,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131344650</v>
+        <v>131344658</v>
       </c>
       <c r="B26" t="n">
-        <v>99022</v>
+        <v>57885</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3303,10 +3307,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552899</v>
+        <v>553131</v>
       </c>
       <c r="R26" t="n">
-        <v>6469774</v>
+        <v>6469899</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3341,13 +3345,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3366,45 +3374,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131344663</v>
+        <v>131344650</v>
       </c>
       <c r="B27" t="n">
-        <v>91838</v>
+        <v>99023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3412,10 +3417,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>553051</v>
+        <v>552899</v>
       </c>
       <c r="R27" t="n">
-        <v>6469833</v>
+        <v>6469774</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3475,10 +3480,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131344658</v>
+        <v>131344663</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>91839</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3486,21 +3491,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3508,13 +3513,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3522,10 +3526,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>553131</v>
+        <v>553051</v>
       </c>
       <c r="R28" t="n">
-        <v>6469899</v>
+        <v>6469833</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3560,17 +3564,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>131344670</v>
       </c>
       <c r="B29" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>131344660</v>
       </c>
       <c r="B30" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>131344653</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3915,42 +3915,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131344704</v>
+        <v>131344666</v>
       </c>
       <c r="B32" t="n">
-        <v>99022</v>
+        <v>57885</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552824</v>
+        <v>553049</v>
       </c>
       <c r="R32" t="n">
-        <v>6469659</v>
+        <v>6469673</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,13 +3996,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4021,42 +4025,46 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131344646</v>
+        <v>131344674</v>
       </c>
       <c r="B33" t="n">
-        <v>99022</v>
+        <v>57885</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4064,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552813</v>
+        <v>552930</v>
       </c>
       <c r="R33" t="n">
-        <v>6469703</v>
+        <v>6469714</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4102,13 +4110,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4127,46 +4139,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131344674</v>
+        <v>131344704</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>99023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4174,10 +4182,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552930</v>
+        <v>552824</v>
       </c>
       <c r="R34" t="n">
-        <v>6469714</v>
+        <v>6469659</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4212,17 +4220,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4241,42 +4245,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131344666</v>
+        <v>131344646</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>99023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4284,10 +4288,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>553049</v>
+        <v>552813</v>
       </c>
       <c r="R35" t="n">
-        <v>6469673</v>
+        <v>6469703</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4322,17 +4326,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>131344680</v>
       </c>
       <c r="B36" t="n">
-        <v>101224</v>
+        <v>101225</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>131344691</v>
       </c>
       <c r="B37" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>131344661</v>
       </c>
       <c r="B38" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>131344659</v>
       </c>
       <c r="B39" t="n">
-        <v>97887</v>
+        <v>97888</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>131344662</v>
       </c>
       <c r="B40" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>131344705</v>
       </c>
       <c r="B41" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>131344645</v>
       </c>
       <c r="B42" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>131344656</v>
       </c>
       <c r="B43" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5208,10 +5208,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131344706</v>
+        <v>131344673</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>58045</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552813</v>
+        <v>552942</v>
       </c>
       <c r="R44" t="n">
-        <v>6469628</v>
+        <v>6469709</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5291,11 +5291,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5322,37 +5317,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131344669</v>
+        <v>131344657</v>
       </c>
       <c r="B45" t="n">
-        <v>99022</v>
+        <v>101225</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -5365,10 +5360,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552952</v>
+        <v>552998</v>
       </c>
       <c r="R45" t="n">
-        <v>6469713</v>
+        <v>6469788</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5428,10 +5423,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131344685</v>
+        <v>131344669</v>
       </c>
       <c r="B46" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,7 +5453,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5471,10 +5466,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552922</v>
+        <v>552952</v>
       </c>
       <c r="R46" t="n">
-        <v>6469668</v>
+        <v>6469713</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5534,10 +5529,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131344675</v>
+        <v>131344685</v>
       </c>
       <c r="B47" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5564,7 +5559,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5577,10 +5572,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552941</v>
+        <v>552922</v>
       </c>
       <c r="R47" t="n">
-        <v>6469708</v>
+        <v>6469668</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5640,10 +5635,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131344667</v>
+        <v>131344675</v>
       </c>
       <c r="B48" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5670,7 +5665,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -5683,10 +5678,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552956</v>
+        <v>552941</v>
       </c>
       <c r="R48" t="n">
-        <v>6469709</v>
+        <v>6469708</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5746,37 +5741,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131344657</v>
+        <v>131344667</v>
       </c>
       <c r="B49" t="n">
-        <v>101224</v>
+        <v>99023</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -5789,10 +5784,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552998</v>
+        <v>552956</v>
       </c>
       <c r="R49" t="n">
-        <v>6469788</v>
+        <v>6469709</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5852,10 +5847,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344673</v>
+        <v>131344706</v>
       </c>
       <c r="B50" t="n">
-        <v>58044</v>
+        <v>57885</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5863,16 +5858,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5899,10 +5894,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552942</v>
+        <v>552813</v>
       </c>
       <c r="R50" t="n">
-        <v>6469709</v>
+        <v>6469628</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5935,6 +5930,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5964,7 +5964,7 @@
         <v>131344655</v>
       </c>
       <c r="B51" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131344679</v>
+        <v>131344654</v>
       </c>
       <c r="B8" t="n">
-        <v>91839</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1354,12 +1354,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552958</v>
+        <v>552967</v>
       </c>
       <c r="R8" t="n">
-        <v>6469695</v>
+        <v>6469782</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,13 +1406,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1430,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131344678</v>
+        <v>131344679</v>
       </c>
       <c r="B9" t="n">
         <v>91839</v>
@@ -1460,7 +1465,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1476,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552948</v>
+        <v>552958</v>
       </c>
       <c r="R9" t="n">
-        <v>6469706</v>
+        <v>6469695</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131344654</v>
+        <v>131344678</v>
       </c>
       <c r="B10" t="n">
-        <v>57885</v>
+        <v>91839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,35 +1555,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1586,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552967</v>
+        <v>552948</v>
       </c>
       <c r="R10" t="n">
-        <v>6469782</v>
+        <v>6469706</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,17 +1628,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1872,37 +1872,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344707</v>
+        <v>131344689</v>
       </c>
       <c r="B13" t="n">
-        <v>101225</v>
+        <v>99023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552818</v>
+        <v>552921</v>
       </c>
       <c r="R13" t="n">
-        <v>6469626</v>
+        <v>6469663</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344689</v>
+        <v>131344647</v>
       </c>
       <c r="B14" t="n">
         <v>99023</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552921</v>
+        <v>552884</v>
       </c>
       <c r="R14" t="n">
-        <v>6469663</v>
+        <v>6469766</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,7 +2084,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344647</v>
+        <v>131344649</v>
       </c>
       <c r="B15" t="n">
         <v>99023</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552884</v>
+        <v>552893</v>
       </c>
       <c r="R15" t="n">
-        <v>6469766</v>
+        <v>6469762</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,37 +2190,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344649</v>
+        <v>131344707</v>
       </c>
       <c r="B16" t="n">
-        <v>99023</v>
+        <v>101225</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552893</v>
+        <v>552818</v>
       </c>
       <c r="R16" t="n">
-        <v>6469762</v>
+        <v>6469626</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131344686</v>
+        <v>131344682</v>
       </c>
       <c r="B17" t="n">
-        <v>79869</v>
+        <v>57885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,21 +2307,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2329,8 +2329,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2338,10 +2343,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552925</v>
+        <v>552956</v>
       </c>
       <c r="R17" t="n">
-        <v>6469645</v>
+        <v>6469666</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,13 +2381,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2401,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344652</v>
+        <v>131344686</v>
       </c>
       <c r="B18" t="n">
-        <v>91839</v>
+        <v>79869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,21 +2421,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2434,11 +2443,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2447,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552916</v>
+        <v>552925</v>
       </c>
       <c r="R18" t="n">
-        <v>6469751</v>
+        <v>6469645</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2510,10 +2515,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344682</v>
+        <v>131344652</v>
       </c>
       <c r="B19" t="n">
-        <v>57885</v>
+        <v>91839</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,21 +2526,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2543,13 +2548,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2557,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552956</v>
+        <v>552916</v>
       </c>
       <c r="R19" t="n">
-        <v>6469666</v>
+        <v>6469751</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,17 +2599,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2624,37 +2624,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344677</v>
+        <v>131344651</v>
       </c>
       <c r="B20" t="n">
-        <v>106144</v>
+        <v>99023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552948</v>
+        <v>552908</v>
       </c>
       <c r="R20" t="n">
-        <v>6469713</v>
+        <v>6469775</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,37 +2730,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344651</v>
+        <v>131344677</v>
       </c>
       <c r="B21" t="n">
-        <v>99023</v>
+        <v>106144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552908</v>
+        <v>552948</v>
       </c>
       <c r="R21" t="n">
-        <v>6469775</v>
+        <v>6469713</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131344666</v>
+        <v>131344674</v>
       </c>
       <c r="B32" t="n">
         <v>57885</v>
@@ -3943,7 +3943,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
@@ -3958,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>553049</v>
+        <v>552930</v>
       </c>
       <c r="R32" t="n">
-        <v>6469673</v>
+        <v>6469714</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4025,7 +4029,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131344674</v>
+        <v>131344666</v>
       </c>
       <c r="B33" t="n">
         <v>57885</v>
@@ -4053,11 +4057,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552930</v>
+        <v>553049</v>
       </c>
       <c r="R33" t="n">
-        <v>6469714</v>
+        <v>6469673</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4563,56 +4563,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131344661</v>
+        <v>131344659</v>
       </c>
       <c r="B38" t="n">
-        <v>91839</v>
+        <v>97888</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>553051</v>
+        <v>553082</v>
       </c>
       <c r="R38" t="n">
-        <v>6469846</v>
+        <v>6469843</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4653,7 +4646,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4672,49 +4664,56 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131344659</v>
+        <v>131344661</v>
       </c>
       <c r="B39" t="n">
-        <v>97888</v>
+        <v>91839</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>553082</v>
+        <v>553051</v>
       </c>
       <c r="R39" t="n">
-        <v>6469843</v>
+        <v>6469846</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4755,6 +4754,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4773,45 +4773,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131344662</v>
+        <v>131344645</v>
       </c>
       <c r="B40" t="n">
-        <v>91839</v>
+        <v>99023</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4819,10 +4816,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>553053</v>
+        <v>552818</v>
       </c>
       <c r="R40" t="n">
-        <v>6469836</v>
+        <v>6469702</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4996,42 +4993,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131344645</v>
+        <v>131344662</v>
       </c>
       <c r="B42" t="n">
-        <v>99023</v>
+        <v>91839</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>552818</v>
+        <v>553053</v>
       </c>
       <c r="R42" t="n">
-        <v>6469702</v>
+        <v>6469836</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5208,46 +5208,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131344673</v>
+        <v>131344669</v>
       </c>
       <c r="B44" t="n">
-        <v>58045</v>
+        <v>99023</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5255,10 +5251,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552942</v>
+        <v>552952</v>
       </c>
       <c r="R44" t="n">
-        <v>6469709</v>
+        <v>6469713</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5299,6 +5295,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5317,37 +5314,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131344657</v>
+        <v>131344685</v>
       </c>
       <c r="B45" t="n">
-        <v>101225</v>
+        <v>99023</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -5360,10 +5357,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552998</v>
+        <v>552922</v>
       </c>
       <c r="R45" t="n">
-        <v>6469788</v>
+        <v>6469668</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5423,7 +5420,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131344669</v>
+        <v>131344675</v>
       </c>
       <c r="B46" t="n">
         <v>99023</v>
@@ -5453,7 +5450,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5466,10 +5463,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552952</v>
+        <v>552941</v>
       </c>
       <c r="R46" t="n">
-        <v>6469713</v>
+        <v>6469708</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5529,7 +5526,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131344685</v>
+        <v>131344667</v>
       </c>
       <c r="B47" t="n">
         <v>99023</v>
@@ -5559,7 +5556,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5572,10 +5569,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552922</v>
+        <v>552956</v>
       </c>
       <c r="R47" t="n">
-        <v>6469668</v>
+        <v>6469709</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5635,37 +5632,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131344675</v>
+        <v>131344657</v>
       </c>
       <c r="B48" t="n">
-        <v>99023</v>
+        <v>101225</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -5678,10 +5675,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552941</v>
+        <v>552998</v>
       </c>
       <c r="R48" t="n">
-        <v>6469708</v>
+        <v>6469788</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5741,42 +5738,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131344667</v>
+        <v>131344706</v>
       </c>
       <c r="B49" t="n">
-        <v>99023</v>
+        <v>57885</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5784,10 +5785,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552956</v>
+        <v>552813</v>
       </c>
       <c r="R49" t="n">
-        <v>6469709</v>
+        <v>6469628</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5822,13 +5823,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5847,10 +5852,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344706</v>
+        <v>131344673</v>
       </c>
       <c r="B50" t="n">
-        <v>57885</v>
+        <v>58045</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5858,16 +5863,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5894,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552813</v>
+        <v>552942</v>
       </c>
       <c r="R50" t="n">
-        <v>6469628</v>
+        <v>6469709</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5930,11 +5935,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131344692</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>131344703</v>
       </c>
       <c r="B4" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>131344676</v>
       </c>
       <c r="B5" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>131344688</v>
       </c>
       <c r="B6" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>131344684</v>
       </c>
       <c r="B7" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,17 +1314,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131344654</v>
+        <v>131344679</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>91842</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1354,13 +1354,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552967</v>
+        <v>552958</v>
       </c>
       <c r="R8" t="n">
-        <v>6469782</v>
+        <v>6469695</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,17 +1405,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1435,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131344679</v>
+        <v>131344678</v>
       </c>
       <c r="B9" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,7 +1460,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1481,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552958</v>
+        <v>552948</v>
       </c>
       <c r="R9" t="n">
-        <v>6469695</v>
+        <v>6469706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131344678</v>
+        <v>131344654</v>
       </c>
       <c r="B10" t="n">
-        <v>91839</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,34 +1550,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1590,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552948</v>
+        <v>552967</v>
       </c>
       <c r="R10" t="n">
-        <v>6469706</v>
+        <v>6469782</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,13 +1624,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>131344696</v>
       </c>
       <c r="B11" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>131344698</v>
       </c>
       <c r="B12" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>131344689</v>
       </c>
       <c r="B13" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>131344647</v>
       </c>
       <c r="B14" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>131344649</v>
       </c>
       <c r="B15" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>131344707</v>
       </c>
       <c r="B16" t="n">
-        <v>101225</v>
+        <v>101228</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131344682</v>
+        <v>131344686</v>
       </c>
       <c r="B17" t="n">
-        <v>57885</v>
+        <v>79872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,21 +2307,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2329,13 +2329,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2343,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552956</v>
+        <v>552925</v>
       </c>
       <c r="R17" t="n">
-        <v>6469666</v>
+        <v>6469645</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,17 +2376,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2410,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344686</v>
+        <v>131344652</v>
       </c>
       <c r="B18" t="n">
-        <v>79869</v>
+        <v>91842</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,21 +2412,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2443,7 +2434,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2452,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552925</v>
+        <v>552916</v>
       </c>
       <c r="R18" t="n">
-        <v>6469645</v>
+        <v>6469751</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2515,10 +2510,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344652</v>
+        <v>131344682</v>
       </c>
       <c r="B19" t="n">
-        <v>91839</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2526,21 +2521,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2548,12 +2543,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2561,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552916</v>
+        <v>552956</v>
       </c>
       <c r="R19" t="n">
-        <v>6469751</v>
+        <v>6469666</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,13 +2595,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344651</v>
+        <v>131344668</v>
       </c>
       <c r="B20" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552908</v>
+        <v>552947</v>
       </c>
       <c r="R20" t="n">
-        <v>6469775</v>
+        <v>6469715</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,7 +2733,7 @@
         <v>131344677</v>
       </c>
       <c r="B21" t="n">
-        <v>106144</v>
+        <v>106148</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131344668</v>
+        <v>131344651</v>
       </c>
       <c r="B22" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552947</v>
+        <v>552908</v>
       </c>
       <c r="R22" t="n">
-        <v>6469715</v>
+        <v>6469775</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2945,7 +2945,7 @@
         <v>131344683</v>
       </c>
       <c r="B23" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>131344687</v>
       </c>
       <c r="B24" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>131344648</v>
       </c>
       <c r="B25" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>131344658</v>
       </c>
       <c r="B26" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3374,42 +3374,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131344650</v>
+        <v>131344663</v>
       </c>
       <c r="B27" t="n">
-        <v>99023</v>
+        <v>91842</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3417,10 +3420,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>552899</v>
+        <v>553051</v>
       </c>
       <c r="R27" t="n">
-        <v>6469774</v>
+        <v>6469833</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3473,52 +3476,49 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131344663</v>
+        <v>131344650</v>
       </c>
       <c r="B28" t="n">
-        <v>91839</v>
+        <v>99026</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>553051</v>
+        <v>552899</v>
       </c>
       <c r="R28" t="n">
-        <v>6469833</v>
+        <v>6469774</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3592,7 +3592,7 @@
         <v>131344670</v>
       </c>
       <c r="B29" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>131344660</v>
       </c>
       <c r="B30" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>131344653</v>
       </c>
       <c r="B31" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>131344674</v>
       </c>
       <c r="B32" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>131344666</v>
       </c>
       <c r="B33" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>131344704</v>
       </c>
       <c r="B34" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>131344646</v>
       </c>
       <c r="B35" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>131344680</v>
       </c>
       <c r="B36" t="n">
-        <v>101225</v>
+        <v>101228</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>131344691</v>
       </c>
       <c r="B37" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4563,49 +4563,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131344659</v>
+        <v>131344661</v>
       </c>
       <c r="B38" t="n">
-        <v>97888</v>
+        <v>91842</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>553082</v>
+        <v>553051</v>
       </c>
       <c r="R38" t="n">
-        <v>6469843</v>
+        <v>6469846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4646,6 +4653,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4664,56 +4672,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131344661</v>
+        <v>131344659</v>
       </c>
       <c r="B39" t="n">
-        <v>91839</v>
+        <v>97891</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>553051</v>
+        <v>553082</v>
       </c>
       <c r="R39" t="n">
-        <v>6469846</v>
+        <v>6469843</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4754,7 +4755,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4773,42 +4773,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131344645</v>
+        <v>131344662</v>
       </c>
       <c r="B40" t="n">
-        <v>99023</v>
+        <v>91842</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4816,10 +4819,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552818</v>
+        <v>553053</v>
       </c>
       <c r="R40" t="n">
-        <v>6469702</v>
+        <v>6469836</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4882,7 +4885,7 @@
         <v>131344705</v>
       </c>
       <c r="B41" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4993,45 +4996,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131344662</v>
+        <v>131344645</v>
       </c>
       <c r="B42" t="n">
-        <v>91839</v>
+        <v>99026</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>553053</v>
+        <v>552818</v>
       </c>
       <c r="R42" t="n">
-        <v>6469836</v>
+        <v>6469702</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5105,7 +5105,7 @@
         <v>131344656</v>
       </c>
       <c r="B43" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5208,42 +5208,46 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131344669</v>
+        <v>131344673</v>
       </c>
       <c r="B44" t="n">
-        <v>99023</v>
+        <v>58048</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5251,10 +5255,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552952</v>
+        <v>552942</v>
       </c>
       <c r="R44" t="n">
-        <v>6469713</v>
+        <v>6469709</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5295,7 +5299,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5314,37 +5317,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131344685</v>
+        <v>131344657</v>
       </c>
       <c r="B45" t="n">
-        <v>99023</v>
+        <v>101228</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -5357,10 +5360,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552922</v>
+        <v>552998</v>
       </c>
       <c r="R45" t="n">
-        <v>6469668</v>
+        <v>6469788</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5420,10 +5423,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131344675</v>
+        <v>131344667</v>
       </c>
       <c r="B46" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5450,7 +5453,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5463,10 +5466,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552941</v>
+        <v>552956</v>
       </c>
       <c r="R46" t="n">
-        <v>6469708</v>
+        <v>6469709</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5526,42 +5529,46 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131344667</v>
+        <v>131344706</v>
       </c>
       <c r="B47" t="n">
-        <v>99023</v>
+        <v>57888</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5569,10 +5576,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552956</v>
+        <v>552813</v>
       </c>
       <c r="R47" t="n">
-        <v>6469709</v>
+        <v>6469628</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5607,13 +5614,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5625,44 +5636,44 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131344657</v>
+        <v>131344669</v>
       </c>
       <c r="B48" t="n">
-        <v>101225</v>
+        <v>99026</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -5675,10 +5686,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552998</v>
+        <v>552952</v>
       </c>
       <c r="R48" t="n">
-        <v>6469788</v>
+        <v>6469713</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5738,46 +5749,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131344706</v>
+        <v>131344685</v>
       </c>
       <c r="B49" t="n">
-        <v>57885</v>
+        <v>99026</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5785,10 +5792,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552813</v>
+        <v>552922</v>
       </c>
       <c r="R49" t="n">
-        <v>6469628</v>
+        <v>6469668</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5823,17 +5830,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5852,46 +5855,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344673</v>
+        <v>131344675</v>
       </c>
       <c r="B50" t="n">
-        <v>58045</v>
+        <v>99026</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5899,10 +5898,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552942</v>
+        <v>552941</v>
       </c>
       <c r="R50" t="n">
-        <v>6469709</v>
+        <v>6469708</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5943,6 +5942,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5964,7 +5964,7 @@
         <v>131344655</v>
       </c>
       <c r="B51" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -792,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131344692</v>
+        <v>131344703</v>
       </c>
       <c r="B3" t="n">
-        <v>79872</v>
+        <v>99027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,6 +827,7 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552907</v>
+        <v>552843</v>
       </c>
       <c r="R3" t="n">
-        <v>6469684</v>
+        <v>6469679</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131344703</v>
+        <v>131344676</v>
       </c>
       <c r="B4" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,7 +928,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -940,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552843</v>
+        <v>552946</v>
       </c>
       <c r="R4" t="n">
-        <v>6469679</v>
+        <v>6469707</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131344676</v>
+        <v>131344688</v>
       </c>
       <c r="B5" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1046,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552946</v>
+        <v>552928</v>
       </c>
       <c r="R5" t="n">
-        <v>6469707</v>
+        <v>6469662</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131344688</v>
+        <v>131344684</v>
       </c>
       <c r="B6" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,7 +1140,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1152,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552928</v>
+        <v>552919</v>
       </c>
       <c r="R6" t="n">
-        <v>6469662</v>
+        <v>6469667</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,42 +1216,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131344684</v>
+        <v>131344692</v>
       </c>
       <c r="B7" t="n">
-        <v>99026</v>
+        <v>79873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552919</v>
+        <v>552907</v>
       </c>
       <c r="R7" t="n">
-        <v>6469667</v>
+        <v>6469684</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,17 +1314,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Emil Ideskär</t>
+          <t>Emil Ideskär, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131344679</v>
+        <v>131344654</v>
       </c>
       <c r="B8" t="n">
-        <v>91842</v>
+        <v>57889</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1354,12 +1354,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552958</v>
+        <v>552967</v>
       </c>
       <c r="R8" t="n">
-        <v>6469695</v>
+        <v>6469782</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,13 +1406,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1430,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131344678</v>
+        <v>131344679</v>
       </c>
       <c r="B9" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,7 +1465,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1476,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552948</v>
+        <v>552958</v>
       </c>
       <c r="R9" t="n">
-        <v>6469706</v>
+        <v>6469695</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131344654</v>
+        <v>131344678</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>91843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,35 +1555,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1586,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552967</v>
+        <v>552948</v>
       </c>
       <c r="R10" t="n">
-        <v>6469782</v>
+        <v>6469706</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,17 +1628,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>131344696</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,41 +1767,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131344698</v>
+        <v>131344689</v>
       </c>
       <c r="B12" t="n">
-        <v>79872</v>
+        <v>99027</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1809,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552887</v>
+        <v>552921</v>
       </c>
       <c r="R12" t="n">
-        <v>6469694</v>
+        <v>6469663</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344689</v>
+        <v>131344647</v>
       </c>
       <c r="B13" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1903,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1915,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552921</v>
+        <v>552884</v>
       </c>
       <c r="R13" t="n">
-        <v>6469663</v>
+        <v>6469766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344647</v>
+        <v>131344649</v>
       </c>
       <c r="B14" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2009,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2021,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552884</v>
+        <v>552893</v>
       </c>
       <c r="R14" t="n">
-        <v>6469766</v>
+        <v>6469762</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,37 +2085,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344649</v>
+        <v>131344707</v>
       </c>
       <c r="B15" t="n">
-        <v>99026</v>
+        <v>101231</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2127,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552893</v>
+        <v>552818</v>
       </c>
       <c r="R15" t="n">
-        <v>6469762</v>
+        <v>6469626</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,42 +2191,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344707</v>
+        <v>131344698</v>
       </c>
       <c r="B16" t="n">
-        <v>101228</v>
+        <v>79873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552818</v>
+        <v>552887</v>
       </c>
       <c r="R16" t="n">
-        <v>6469626</v>
+        <v>6469694</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131344686</v>
+        <v>131344682</v>
       </c>
       <c r="B17" t="n">
-        <v>79872</v>
+        <v>57889</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,21 +2307,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2329,8 +2329,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2338,10 +2343,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552925</v>
+        <v>552956</v>
       </c>
       <c r="R17" t="n">
-        <v>6469645</v>
+        <v>6469666</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,13 +2381,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2401,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344652</v>
+        <v>131344686</v>
       </c>
       <c r="B18" t="n">
-        <v>91842</v>
+        <v>79873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,21 +2421,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2434,11 +2443,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2447,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552916</v>
+        <v>552925</v>
       </c>
       <c r="R18" t="n">
-        <v>6469751</v>
+        <v>6469645</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2510,10 +2515,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344682</v>
+        <v>131344652</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>91843</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,21 +2526,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2543,13 +2548,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2557,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552956</v>
+        <v>552916</v>
       </c>
       <c r="R19" t="n">
-        <v>6469666</v>
+        <v>6469751</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,17 +2599,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Emil Ideskär</t>
+          <t>Emil Ideskär, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344668</v>
+        <v>131344651</v>
       </c>
       <c r="B20" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552947</v>
+        <v>552908</v>
       </c>
       <c r="R20" t="n">
-        <v>6469715</v>
+        <v>6469775</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,37 +2730,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344677</v>
+        <v>131344668</v>
       </c>
       <c r="B21" t="n">
-        <v>106148</v>
+        <v>99027</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552948</v>
+        <v>552947</v>
       </c>
       <c r="R21" t="n">
-        <v>6469713</v>
+        <v>6469715</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,37 +2836,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131344651</v>
+        <v>131344677</v>
       </c>
       <c r="B22" t="n">
-        <v>99026</v>
+        <v>106153</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552908</v>
+        <v>552948</v>
       </c>
       <c r="R22" t="n">
-        <v>6469775</v>
+        <v>6469713</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2945,7 +2945,7 @@
         <v>131344683</v>
       </c>
       <c r="B23" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>131344687</v>
       </c>
       <c r="B24" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>131344648</v>
       </c>
       <c r="B25" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>131344658</v>
       </c>
       <c r="B26" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>131344663</v>
       </c>
       <c r="B27" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Emil Ideskär</t>
+          <t>Emil Ideskär, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3486,7 +3486,7 @@
         <v>131344650</v>
       </c>
       <c r="B28" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>131344670</v>
       </c>
       <c r="B29" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>131344660</v>
       </c>
       <c r="B30" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>131344653</v>
       </c>
       <c r="B31" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>131344674</v>
       </c>
       <c r="B32" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>131344666</v>
       </c>
       <c r="B33" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>131344704</v>
       </c>
       <c r="B34" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>131344646</v>
       </c>
       <c r="B35" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>131344680</v>
       </c>
       <c r="B36" t="n">
-        <v>101228</v>
+        <v>101231</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>131344691</v>
       </c>
       <c r="B37" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>131344661</v>
       </c>
       <c r="B38" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>131344659</v>
       </c>
       <c r="B39" t="n">
-        <v>97891</v>
+        <v>97892</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>131344662</v>
       </c>
       <c r="B40" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>131344705</v>
       </c>
       <c r="B41" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>131344645</v>
       </c>
       <c r="B42" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>131344656</v>
       </c>
       <c r="B43" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5208,10 +5208,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131344673</v>
+        <v>131344706</v>
       </c>
       <c r="B44" t="n">
-        <v>58048</v>
+        <v>57889</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552942</v>
+        <v>552813</v>
       </c>
       <c r="R44" t="n">
-        <v>6469709</v>
+        <v>6469628</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5291,6 +5291,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5317,42 +5322,46 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131344657</v>
+        <v>131344673</v>
       </c>
       <c r="B45" t="n">
-        <v>101228</v>
+        <v>58049</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>103020</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5360,10 +5369,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552998</v>
+        <v>552942</v>
       </c>
       <c r="R45" t="n">
-        <v>6469788</v>
+        <v>6469709</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5404,7 +5413,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5423,10 +5431,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131344667</v>
+        <v>131344669</v>
       </c>
       <c r="B46" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5453,7 +5461,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5466,10 +5474,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552956</v>
+        <v>552952</v>
       </c>
       <c r="R46" t="n">
-        <v>6469709</v>
+        <v>6469713</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5529,46 +5537,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131344706</v>
+        <v>131344685</v>
       </c>
       <c r="B47" t="n">
-        <v>57888</v>
+        <v>99027</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5576,10 +5580,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552813</v>
+        <v>552922</v>
       </c>
       <c r="R47" t="n">
-        <v>6469628</v>
+        <v>6469668</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5614,17 +5618,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5636,17 +5636,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Emil Ideskär</t>
+          <t>Emil Ideskär, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131344669</v>
+        <v>131344675</v>
       </c>
       <c r="B48" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -5686,10 +5686,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552952</v>
+        <v>552941</v>
       </c>
       <c r="R48" t="n">
-        <v>6469713</v>
+        <v>6469708</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5749,10 +5749,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131344685</v>
+        <v>131344667</v>
       </c>
       <c r="B49" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552922</v>
+        <v>552956</v>
       </c>
       <c r="R49" t="n">
-        <v>6469668</v>
+        <v>6469709</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5855,37 +5855,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344675</v>
+        <v>131344657</v>
       </c>
       <c r="B50" t="n">
-        <v>99026</v>
+        <v>101231</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -5898,10 +5898,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552941</v>
+        <v>552998</v>
       </c>
       <c r="R50" t="n">
-        <v>6469708</v>
+        <v>6469788</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5964,7 +5964,7 @@
         <v>131344655</v>
       </c>
       <c r="B51" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -792,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131344703</v>
+        <v>131344692</v>
       </c>
       <c r="B3" t="n">
-        <v>99027</v>
+        <v>79879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,7 +827,6 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552843</v>
+        <v>552907</v>
       </c>
       <c r="R3" t="n">
-        <v>6469679</v>
+        <v>6469684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131344676</v>
+        <v>131344703</v>
       </c>
       <c r="B4" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -941,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552946</v>
+        <v>552843</v>
       </c>
       <c r="R4" t="n">
-        <v>6469707</v>
+        <v>6469679</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131344688</v>
+        <v>131344676</v>
       </c>
       <c r="B5" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,7 +1033,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1047,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552928</v>
+        <v>552946</v>
       </c>
       <c r="R5" t="n">
-        <v>6469662</v>
+        <v>6469707</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131344684</v>
+        <v>131344688</v>
       </c>
       <c r="B6" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,7 +1139,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1153,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552919</v>
+        <v>552928</v>
       </c>
       <c r="R6" t="n">
-        <v>6469667</v>
+        <v>6469662</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,41 +1215,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131344692</v>
+        <v>131344684</v>
       </c>
       <c r="B7" t="n">
-        <v>79873</v>
+        <v>99033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552907</v>
+        <v>552919</v>
       </c>
       <c r="R7" t="n">
-        <v>6469684</v>
+        <v>6469667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131344654</v>
+        <v>131344679</v>
       </c>
       <c r="B8" t="n">
-        <v>57889</v>
+        <v>91849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1354,13 +1354,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552967</v>
+        <v>552958</v>
       </c>
       <c r="R8" t="n">
-        <v>6469782</v>
+        <v>6469695</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,17 +1405,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1435,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131344679</v>
+        <v>131344678</v>
       </c>
       <c r="B9" t="n">
-        <v>91843</v>
+        <v>91849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,7 +1460,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1481,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552958</v>
+        <v>552948</v>
       </c>
       <c r="R9" t="n">
-        <v>6469695</v>
+        <v>6469706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131344678</v>
+        <v>131344654</v>
       </c>
       <c r="B10" t="n">
-        <v>91843</v>
+        <v>57895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,34 +1550,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1590,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552948</v>
+        <v>552967</v>
       </c>
       <c r="R10" t="n">
-        <v>6469706</v>
+        <v>6469782</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,13 +1624,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>131344696</v>
       </c>
       <c r="B11" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,42 +1767,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131344689</v>
+        <v>131344698</v>
       </c>
       <c r="B12" t="n">
-        <v>99027</v>
+        <v>79879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1810,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552921</v>
+        <v>552887</v>
       </c>
       <c r="R12" t="n">
-        <v>6469663</v>
+        <v>6469694</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344647</v>
+        <v>131344689</v>
       </c>
       <c r="B13" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,7 +1902,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1916,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552884</v>
+        <v>552921</v>
       </c>
       <c r="R13" t="n">
-        <v>6469766</v>
+        <v>6469663</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344649</v>
+        <v>131344647</v>
       </c>
       <c r="B14" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2008,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2022,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552893</v>
+        <v>552884</v>
       </c>
       <c r="R14" t="n">
-        <v>6469762</v>
+        <v>6469766</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,37 +2084,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344707</v>
+        <v>131344649</v>
       </c>
       <c r="B15" t="n">
-        <v>101231</v>
+        <v>99033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2128,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552818</v>
+        <v>552893</v>
       </c>
       <c r="R15" t="n">
-        <v>6469626</v>
+        <v>6469762</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,41 +2190,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344698</v>
+        <v>131344707</v>
       </c>
       <c r="B16" t="n">
-        <v>79873</v>
+        <v>101237</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552887</v>
+        <v>552818</v>
       </c>
       <c r="R16" t="n">
-        <v>6469694</v>
+        <v>6469626</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131344682</v>
+        <v>131344652</v>
       </c>
       <c r="B17" t="n">
-        <v>57889</v>
+        <v>91849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,21 +2307,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2329,13 +2329,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2343,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552956</v>
+        <v>552916</v>
       </c>
       <c r="R17" t="n">
-        <v>6469666</v>
+        <v>6469751</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,17 +2380,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2413,7 +2408,7 @@
         <v>131344686</v>
       </c>
       <c r="B18" t="n">
-        <v>79873</v>
+        <v>79879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2515,10 +2510,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344652</v>
+        <v>131344682</v>
       </c>
       <c r="B19" t="n">
-        <v>91843</v>
+        <v>57895</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2526,21 +2521,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2548,12 +2543,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2561,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552916</v>
+        <v>552956</v>
       </c>
       <c r="R19" t="n">
-        <v>6469751</v>
+        <v>6469666</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,13 +2595,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>131344651</v>
       </c>
       <c r="B20" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,37 +2730,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344668</v>
+        <v>131344677</v>
       </c>
       <c r="B21" t="n">
-        <v>99027</v>
+        <v>106159</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552947</v>
+        <v>552948</v>
       </c>
       <c r="R21" t="n">
-        <v>6469715</v>
+        <v>6469713</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,37 +2836,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131344677</v>
+        <v>131344668</v>
       </c>
       <c r="B22" t="n">
-        <v>106153</v>
+        <v>99033</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552948</v>
+        <v>552947</v>
       </c>
       <c r="R22" t="n">
-        <v>6469713</v>
+        <v>6469715</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2945,7 +2945,7 @@
         <v>131344683</v>
       </c>
       <c r="B23" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>131344687</v>
       </c>
       <c r="B24" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>131344648</v>
       </c>
       <c r="B25" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,46 +3260,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131344658</v>
+        <v>131344650</v>
       </c>
       <c r="B26" t="n">
-        <v>57889</v>
+        <v>99033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3307,10 +3303,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>553131</v>
+        <v>552899</v>
       </c>
       <c r="R26" t="n">
-        <v>6469899</v>
+        <v>6469774</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3345,17 +3341,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3377,7 +3369,7 @@
         <v>131344663</v>
       </c>
       <c r="B27" t="n">
-        <v>91843</v>
+        <v>91849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3483,42 +3475,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131344650</v>
+        <v>131344658</v>
       </c>
       <c r="B28" t="n">
-        <v>99027</v>
+        <v>57895</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3526,10 +3522,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>552899</v>
+        <v>553131</v>
       </c>
       <c r="R28" t="n">
-        <v>6469774</v>
+        <v>6469899</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3564,13 +3560,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>131344670</v>
       </c>
       <c r="B29" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>131344660</v>
       </c>
       <c r="B30" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>131344653</v>
       </c>
       <c r="B31" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>131344674</v>
       </c>
       <c r="B32" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>131344666</v>
       </c>
       <c r="B33" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>131344704</v>
       </c>
       <c r="B34" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>131344646</v>
       </c>
       <c r="B35" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>131344680</v>
       </c>
       <c r="B36" t="n">
-        <v>101231</v>
+        <v>101237</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>131344691</v>
       </c>
       <c r="B37" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>131344661</v>
       </c>
       <c r="B38" t="n">
-        <v>91843</v>
+        <v>91849</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>131344659</v>
       </c>
       <c r="B39" t="n">
-        <v>97892</v>
+        <v>97898</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>131344662</v>
       </c>
       <c r="B40" t="n">
-        <v>91843</v>
+        <v>91849</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>131344705</v>
       </c>
       <c r="B41" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>131344645</v>
       </c>
       <c r="B42" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>131344656</v>
       </c>
       <c r="B43" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5208,10 +5208,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131344706</v>
+        <v>131344673</v>
       </c>
       <c r="B44" t="n">
-        <v>57889</v>
+        <v>58055</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552813</v>
+        <v>552942</v>
       </c>
       <c r="R44" t="n">
-        <v>6469628</v>
+        <v>6469709</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5291,11 +5291,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5322,10 +5317,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131344673</v>
+        <v>131344706</v>
       </c>
       <c r="B45" t="n">
-        <v>58049</v>
+        <v>57895</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5333,16 +5328,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5369,10 +5364,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552942</v>
+        <v>552813</v>
       </c>
       <c r="R45" t="n">
-        <v>6469709</v>
+        <v>6469628</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5405,6 +5400,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5434,7 +5434,7 @@
         <v>131344669</v>
       </c>
       <c r="B46" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>131344685</v>
       </c>
       <c r="B47" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>131344675</v>
       </c>
       <c r="B48" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>131344667</v>
       </c>
       <c r="B49" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>131344657</v>
       </c>
       <c r="B50" t="n">
-        <v>101231</v>
+        <v>101237</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>131344655</v>
       </c>
       <c r="B51" t="n">
-        <v>91843</v>
+        <v>91849</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -792,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131344692</v>
+        <v>131344703</v>
       </c>
       <c r="B3" t="n">
-        <v>79879</v>
+        <v>99033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,6 +827,7 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552907</v>
+        <v>552843</v>
       </c>
       <c r="R3" t="n">
-        <v>6469684</v>
+        <v>6469679</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131344703</v>
+        <v>131344676</v>
       </c>
       <c r="B4" t="n">
         <v>99033</v>
@@ -927,7 +928,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -940,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552843</v>
+        <v>552946</v>
       </c>
       <c r="R4" t="n">
-        <v>6469679</v>
+        <v>6469707</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1004,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131344676</v>
+        <v>131344688</v>
       </c>
       <c r="B5" t="n">
         <v>99033</v>
@@ -1033,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1046,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552946</v>
+        <v>552928</v>
       </c>
       <c r="R5" t="n">
-        <v>6469707</v>
+        <v>6469662</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131344688</v>
+        <v>131344684</v>
       </c>
       <c r="B6" t="n">
         <v>99033</v>
@@ -1139,7 +1140,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1152,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552928</v>
+        <v>552919</v>
       </c>
       <c r="R6" t="n">
-        <v>6469662</v>
+        <v>6469667</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,42 +1216,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131344684</v>
+        <v>131344692</v>
       </c>
       <c r="B7" t="n">
-        <v>99033</v>
+        <v>79879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552919</v>
+        <v>552907</v>
       </c>
       <c r="R7" t="n">
-        <v>6469667</v>
+        <v>6469684</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1767,41 +1767,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131344698</v>
+        <v>131344689</v>
       </c>
       <c r="B12" t="n">
-        <v>79879</v>
+        <v>99033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1809,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552887</v>
+        <v>552921</v>
       </c>
       <c r="R12" t="n">
-        <v>6469694</v>
+        <v>6469663</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,7 +1873,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344689</v>
+        <v>131344647</v>
       </c>
       <c r="B13" t="n">
         <v>99033</v>
@@ -1902,7 +1903,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1915,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552921</v>
+        <v>552884</v>
       </c>
       <c r="R13" t="n">
-        <v>6469663</v>
+        <v>6469766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,7 +1979,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344647</v>
+        <v>131344649</v>
       </c>
       <c r="B14" t="n">
         <v>99033</v>
@@ -2008,7 +2009,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2021,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552884</v>
+        <v>552893</v>
       </c>
       <c r="R14" t="n">
-        <v>6469766</v>
+        <v>6469762</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,42 +2085,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344649</v>
+        <v>131344698</v>
       </c>
       <c r="B15" t="n">
-        <v>99033</v>
+        <v>79879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552893</v>
+        <v>552887</v>
       </c>
       <c r="R15" t="n">
-        <v>6469762</v>
+        <v>6469694</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131344652</v>
+        <v>131344686</v>
       </c>
       <c r="B17" t="n">
-        <v>91849</v>
+        <v>79879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,21 +2307,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2329,11 +2329,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2342,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552916</v>
+        <v>552925</v>
       </c>
       <c r="R17" t="n">
-        <v>6469751</v>
+        <v>6469645</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2405,41 +2401,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344686</v>
+        <v>131344651</v>
       </c>
       <c r="B18" t="n">
-        <v>79879</v>
+        <v>99033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2447,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552925</v>
+        <v>552908</v>
       </c>
       <c r="R18" t="n">
-        <v>6469645</v>
+        <v>6469775</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2510,46 +2507,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344682</v>
+        <v>131344677</v>
       </c>
       <c r="B19" t="n">
-        <v>57895</v>
+        <v>106159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2557,10 +2550,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552956</v>
+        <v>552948</v>
       </c>
       <c r="R19" t="n">
-        <v>6469666</v>
+        <v>6469713</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,17 +2588,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2624,7 +2613,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344651</v>
+        <v>131344668</v>
       </c>
       <c r="B20" t="n">
         <v>99033</v>
@@ -2654,7 +2643,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2667,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552908</v>
+        <v>552947</v>
       </c>
       <c r="R20" t="n">
-        <v>6469775</v>
+        <v>6469715</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,42 +2719,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344677</v>
+        <v>131344652</v>
       </c>
       <c r="B21" t="n">
-        <v>106159</v>
+        <v>91849</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2773,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552948</v>
+        <v>552916</v>
       </c>
       <c r="R21" t="n">
-        <v>6469713</v>
+        <v>6469751</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,42 +2828,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131344668</v>
+        <v>131344682</v>
       </c>
       <c r="B22" t="n">
-        <v>99033</v>
+        <v>57895</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2879,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552947</v>
+        <v>552956</v>
       </c>
       <c r="R22" t="n">
-        <v>6469715</v>
+        <v>6469666</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2917,13 +2913,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -4773,45 +4773,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131344662</v>
+        <v>131344645</v>
       </c>
       <c r="B40" t="n">
-        <v>91849</v>
+        <v>99033</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4819,10 +4816,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>553053</v>
+        <v>552818</v>
       </c>
       <c r="R40" t="n">
-        <v>6469836</v>
+        <v>6469702</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4882,10 +4879,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131344705</v>
+        <v>131344662</v>
       </c>
       <c r="B41" t="n">
-        <v>57895</v>
+        <v>91849</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4893,21 +4890,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4915,13 +4912,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4929,10 +4925,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>552781</v>
+        <v>553053</v>
       </c>
       <c r="R41" t="n">
-        <v>6469669</v>
+        <v>6469836</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4967,17 +4963,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4996,42 +4988,46 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131344645</v>
+        <v>131344705</v>
       </c>
       <c r="B42" t="n">
-        <v>99033</v>
+        <v>57895</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5039,10 +5035,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>552818</v>
+        <v>552781</v>
       </c>
       <c r="R42" t="n">
-        <v>6469702</v>
+        <v>6469669</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5077,13 +5073,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5208,10 +5208,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131344673</v>
+        <v>131344706</v>
       </c>
       <c r="B44" t="n">
-        <v>58055</v>
+        <v>57895</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552942</v>
+        <v>552813</v>
       </c>
       <c r="R44" t="n">
-        <v>6469709</v>
+        <v>6469628</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5291,6 +5291,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5317,46 +5322,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131344706</v>
+        <v>131344669</v>
       </c>
       <c r="B45" t="n">
-        <v>57895</v>
+        <v>99033</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5364,10 +5365,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552813</v>
+        <v>552952</v>
       </c>
       <c r="R45" t="n">
-        <v>6469628</v>
+        <v>6469713</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5402,17 +5403,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5431,7 +5428,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131344669</v>
+        <v>131344685</v>
       </c>
       <c r="B46" t="n">
         <v>99033</v>
@@ -5461,7 +5458,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5474,10 +5471,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552952</v>
+        <v>552922</v>
       </c>
       <c r="R46" t="n">
-        <v>6469713</v>
+        <v>6469668</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5537,7 +5534,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131344685</v>
+        <v>131344675</v>
       </c>
       <c r="B47" t="n">
         <v>99033</v>
@@ -5567,7 +5564,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5580,10 +5577,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552922</v>
+        <v>552941</v>
       </c>
       <c r="R47" t="n">
-        <v>6469668</v>
+        <v>6469708</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5643,7 +5640,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131344675</v>
+        <v>131344667</v>
       </c>
       <c r="B48" t="n">
         <v>99033</v>
@@ -5673,7 +5670,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -5686,10 +5683,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552941</v>
+        <v>552956</v>
       </c>
       <c r="R48" t="n">
-        <v>6469708</v>
+        <v>6469709</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5749,37 +5746,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131344667</v>
+        <v>131344657</v>
       </c>
       <c r="B49" t="n">
-        <v>99033</v>
+        <v>101237</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -5792,10 +5789,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552956</v>
+        <v>552998</v>
       </c>
       <c r="R49" t="n">
-        <v>6469709</v>
+        <v>6469788</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5855,42 +5852,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344657</v>
+        <v>131344673</v>
       </c>
       <c r="B50" t="n">
-        <v>101237</v>
+        <v>58055</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>103020</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5898,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552998</v>
+        <v>552942</v>
       </c>
       <c r="R50" t="n">
-        <v>6469788</v>
+        <v>6469709</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5942,7 +5943,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -2085,41 +2085,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344698</v>
+        <v>131344707</v>
       </c>
       <c r="B15" t="n">
-        <v>79879</v>
+        <v>101237</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2127,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552887</v>
+        <v>552818</v>
       </c>
       <c r="R15" t="n">
-        <v>6469694</v>
+        <v>6469626</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,42 +2191,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344707</v>
+        <v>131344698</v>
       </c>
       <c r="B16" t="n">
-        <v>101237</v>
+        <v>79879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552818</v>
+        <v>552887</v>
       </c>
       <c r="R16" t="n">
-        <v>6469626</v>
+        <v>6469694</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2401,42 +2401,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344651</v>
+        <v>131344682</v>
       </c>
       <c r="B18" t="n">
-        <v>99033</v>
+        <v>57895</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2444,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552908</v>
+        <v>552956</v>
       </c>
       <c r="R18" t="n">
-        <v>6469775</v>
+        <v>6469666</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,13 +2486,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2507,42 +2515,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344677</v>
+        <v>131344652</v>
       </c>
       <c r="B19" t="n">
-        <v>106159</v>
+        <v>91849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2550,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552948</v>
+        <v>552916</v>
       </c>
       <c r="R19" t="n">
-        <v>6469713</v>
+        <v>6469751</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2613,7 +2624,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344668</v>
+        <v>131344651</v>
       </c>
       <c r="B20" t="n">
         <v>99033</v>
@@ -2643,7 +2654,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2656,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552947</v>
+        <v>552908</v>
       </c>
       <c r="R20" t="n">
-        <v>6469715</v>
+        <v>6469775</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2719,45 +2730,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344652</v>
+        <v>131344677</v>
       </c>
       <c r="B21" t="n">
-        <v>91849</v>
+        <v>106159</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2765,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552916</v>
+        <v>552948</v>
       </c>
       <c r="R21" t="n">
-        <v>6469751</v>
+        <v>6469713</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,46 +2836,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131344682</v>
+        <v>131344668</v>
       </c>
       <c r="B22" t="n">
-        <v>57895</v>
+        <v>99033</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2875,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552956</v>
+        <v>552947</v>
       </c>
       <c r="R22" t="n">
-        <v>6469666</v>
+        <v>6469715</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,17 +2917,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3260,42 +3260,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131344650</v>
+        <v>131344658</v>
       </c>
       <c r="B26" t="n">
-        <v>99033</v>
+        <v>57895</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3303,10 +3307,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552899</v>
+        <v>553131</v>
       </c>
       <c r="R26" t="n">
-        <v>6469774</v>
+        <v>6469899</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3341,13 +3345,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3475,46 +3483,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131344658</v>
+        <v>131344650</v>
       </c>
       <c r="B28" t="n">
-        <v>57895</v>
+        <v>99033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3522,10 +3526,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>553131</v>
+        <v>552899</v>
       </c>
       <c r="R28" t="n">
-        <v>6469899</v>
+        <v>6469774</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3560,17 +3564,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4563,56 +4563,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131344661</v>
+        <v>131344659</v>
       </c>
       <c r="B38" t="n">
-        <v>91849</v>
+        <v>97898</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>553051</v>
+        <v>553082</v>
       </c>
       <c r="R38" t="n">
-        <v>6469846</v>
+        <v>6469843</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4653,7 +4646,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4672,49 +4664,56 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131344659</v>
+        <v>131344661</v>
       </c>
       <c r="B39" t="n">
-        <v>97898</v>
+        <v>91849</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>553082</v>
+        <v>553051</v>
       </c>
       <c r="R39" t="n">
-        <v>6469843</v>
+        <v>6469846</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4755,6 +4754,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4773,42 +4773,46 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131344645</v>
+        <v>131344705</v>
       </c>
       <c r="B40" t="n">
-        <v>99033</v>
+        <v>57895</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4816,10 +4820,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552818</v>
+        <v>552781</v>
       </c>
       <c r="R40" t="n">
-        <v>6469702</v>
+        <v>6469669</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4854,13 +4858,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4988,46 +4996,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131344705</v>
+        <v>131344645</v>
       </c>
       <c r="B42" t="n">
-        <v>57895</v>
+        <v>99033</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5035,10 +5039,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>552781</v>
+        <v>552818</v>
       </c>
       <c r="R42" t="n">
-        <v>6469669</v>
+        <v>6469702</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,17 +5077,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131344679</v>
+        <v>131344654</v>
       </c>
       <c r="B8" t="n">
-        <v>91849</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1354,12 +1354,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552958</v>
+        <v>552967</v>
       </c>
       <c r="R8" t="n">
-        <v>6469695</v>
+        <v>6469782</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,13 +1406,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1430,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131344678</v>
+        <v>131344679</v>
       </c>
       <c r="B9" t="n">
         <v>91849</v>
@@ -1460,7 +1465,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1476,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552948</v>
+        <v>552958</v>
       </c>
       <c r="R9" t="n">
-        <v>6469706</v>
+        <v>6469695</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131344654</v>
+        <v>131344678</v>
       </c>
       <c r="B10" t="n">
-        <v>57895</v>
+        <v>91849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,35 +1555,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1586,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552967</v>
+        <v>552948</v>
       </c>
       <c r="R10" t="n">
-        <v>6469782</v>
+        <v>6469706</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,17 +1628,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1767,42 +1767,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131344689</v>
+        <v>131344698</v>
       </c>
       <c r="B12" t="n">
-        <v>99033</v>
+        <v>79879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1810,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552921</v>
+        <v>552887</v>
       </c>
       <c r="R12" t="n">
-        <v>6469663</v>
+        <v>6469694</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,7 +1872,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344647</v>
+        <v>131344689</v>
       </c>
       <c r="B13" t="n">
         <v>99033</v>
@@ -1903,7 +1902,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1916,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552884</v>
+        <v>552921</v>
       </c>
       <c r="R13" t="n">
-        <v>6469766</v>
+        <v>6469663</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,7 +1978,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344649</v>
+        <v>131344647</v>
       </c>
       <c r="B14" t="n">
         <v>99033</v>
@@ -2009,7 +2008,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2022,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552893</v>
+        <v>552884</v>
       </c>
       <c r="R14" t="n">
-        <v>6469762</v>
+        <v>6469766</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,37 +2084,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344707</v>
+        <v>131344649</v>
       </c>
       <c r="B15" t="n">
-        <v>101237</v>
+        <v>99033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2128,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552818</v>
+        <v>552893</v>
       </c>
       <c r="R15" t="n">
-        <v>6469626</v>
+        <v>6469762</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,41 +2190,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344698</v>
+        <v>131344707</v>
       </c>
       <c r="B16" t="n">
-        <v>79879</v>
+        <v>101237</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552887</v>
+        <v>552818</v>
       </c>
       <c r="R16" t="n">
-        <v>6469694</v>
+        <v>6469626</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -4563,49 +4563,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131344659</v>
+        <v>131344661</v>
       </c>
       <c r="B38" t="n">
-        <v>97898</v>
+        <v>91849</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>553082</v>
+        <v>553051</v>
       </c>
       <c r="R38" t="n">
-        <v>6469843</v>
+        <v>6469846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4646,6 +4653,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4664,56 +4672,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131344661</v>
+        <v>131344659</v>
       </c>
       <c r="B39" t="n">
-        <v>91849</v>
+        <v>97898</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>553051</v>
+        <v>553082</v>
       </c>
       <c r="R39" t="n">
-        <v>6469846</v>
+        <v>6469843</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4754,7 +4755,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4773,46 +4773,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131344705</v>
+        <v>131344645</v>
       </c>
       <c r="B40" t="n">
-        <v>57895</v>
+        <v>99033</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4820,10 +4816,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552781</v>
+        <v>552818</v>
       </c>
       <c r="R40" t="n">
-        <v>6469669</v>
+        <v>6469702</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4858,17 +4854,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4887,10 +4879,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131344662</v>
+        <v>131344705</v>
       </c>
       <c r="B41" t="n">
-        <v>91849</v>
+        <v>57895</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4898,21 +4890,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4920,12 +4912,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4933,10 +4926,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>553053</v>
+        <v>552781</v>
       </c>
       <c r="R41" t="n">
-        <v>6469836</v>
+        <v>6469669</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4971,13 +4964,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4996,42 +4993,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131344645</v>
+        <v>131344662</v>
       </c>
       <c r="B42" t="n">
-        <v>99033</v>
+        <v>91849</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>552818</v>
+        <v>553053</v>
       </c>
       <c r="R42" t="n">
-        <v>6469702</v>
+        <v>6469836</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5322,42 +5322,46 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131344669</v>
+        <v>131344673</v>
       </c>
       <c r="B45" t="n">
-        <v>99033</v>
+        <v>58055</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5365,10 +5369,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552952</v>
+        <v>552942</v>
       </c>
       <c r="R45" t="n">
-        <v>6469713</v>
+        <v>6469709</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5409,7 +5413,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5428,7 +5431,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131344685</v>
+        <v>131344669</v>
       </c>
       <c r="B46" t="n">
         <v>99033</v>
@@ -5458,7 +5461,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5471,10 +5474,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552922</v>
+        <v>552952</v>
       </c>
       <c r="R46" t="n">
-        <v>6469668</v>
+        <v>6469713</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5534,7 +5537,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131344675</v>
+        <v>131344685</v>
       </c>
       <c r="B47" t="n">
         <v>99033</v>
@@ -5564,7 +5567,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5577,10 +5580,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552941</v>
+        <v>552922</v>
       </c>
       <c r="R47" t="n">
-        <v>6469708</v>
+        <v>6469668</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5640,7 +5643,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131344667</v>
+        <v>131344675</v>
       </c>
       <c r="B48" t="n">
         <v>99033</v>
@@ -5670,7 +5673,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -5683,10 +5686,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552956</v>
+        <v>552941</v>
       </c>
       <c r="R48" t="n">
-        <v>6469709</v>
+        <v>6469708</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5746,37 +5749,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131344657</v>
+        <v>131344667</v>
       </c>
       <c r="B49" t="n">
-        <v>101237</v>
+        <v>99033</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -5789,10 +5792,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552998</v>
+        <v>552956</v>
       </c>
       <c r="R49" t="n">
-        <v>6469788</v>
+        <v>6469709</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5852,46 +5855,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344673</v>
+        <v>131344657</v>
       </c>
       <c r="B50" t="n">
-        <v>58055</v>
+        <v>101237</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103020</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5899,10 +5898,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552942</v>
+        <v>552998</v>
       </c>
       <c r="R50" t="n">
-        <v>6469709</v>
+        <v>6469788</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5943,6 +5942,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131344703</v>
       </c>
       <c r="B3" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>131344676</v>
       </c>
       <c r="B4" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>131344688</v>
       </c>
       <c r="B5" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131344684</v>
       </c>
       <c r="B6" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131344654</v>
+        <v>131344679</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>91849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1354,13 +1354,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552967</v>
+        <v>552958</v>
       </c>
       <c r="R8" t="n">
-        <v>6469782</v>
+        <v>6469695</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,17 +1405,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1435,7 +1430,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131344679</v>
+        <v>131344678</v>
       </c>
       <c r="B9" t="n">
         <v>91849</v>
@@ -1465,7 +1460,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1481,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552958</v>
+        <v>552948</v>
       </c>
       <c r="R9" t="n">
-        <v>6469695</v>
+        <v>6469706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131344678</v>
+        <v>131344654</v>
       </c>
       <c r="B10" t="n">
-        <v>91849</v>
+        <v>57895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,34 +1550,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1590,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552948</v>
+        <v>552967</v>
       </c>
       <c r="R10" t="n">
-        <v>6469706</v>
+        <v>6469782</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,13 +1624,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344689</v>
+        <v>131344647</v>
       </c>
       <c r="B13" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552921</v>
+        <v>552884</v>
       </c>
       <c r="R13" t="n">
-        <v>6469663</v>
+        <v>6469766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,37 +1978,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344647</v>
+        <v>131344707</v>
       </c>
       <c r="B14" t="n">
-        <v>99033</v>
+        <v>101238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552884</v>
+        <v>552818</v>
       </c>
       <c r="R14" t="n">
-        <v>6469766</v>
+        <v>6469626</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344649</v>
+        <v>131344689</v>
       </c>
       <c r="B15" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552893</v>
+        <v>552921</v>
       </c>
       <c r="R15" t="n">
-        <v>6469762</v>
+        <v>6469663</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,37 +2190,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344707</v>
+        <v>131344649</v>
       </c>
       <c r="B16" t="n">
-        <v>101237</v>
+        <v>99034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552818</v>
+        <v>552893</v>
       </c>
       <c r="R16" t="n">
-        <v>6469626</v>
+        <v>6469762</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344682</v>
+        <v>131344652</v>
       </c>
       <c r="B18" t="n">
-        <v>57895</v>
+        <v>91849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,21 +2412,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2434,13 +2434,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2448,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552956</v>
+        <v>552916</v>
       </c>
       <c r="R18" t="n">
-        <v>6469666</v>
+        <v>6469751</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,17 +2485,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2515,10 +2510,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344652</v>
+        <v>131344682</v>
       </c>
       <c r="B19" t="n">
-        <v>91849</v>
+        <v>57895</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2526,21 +2521,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2548,12 +2543,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2561,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552916</v>
+        <v>552956</v>
       </c>
       <c r="R19" t="n">
-        <v>6469751</v>
+        <v>6469666</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,13 +2595,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2624,37 +2624,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344651</v>
+        <v>131344677</v>
       </c>
       <c r="B20" t="n">
-        <v>99033</v>
+        <v>106160</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552908</v>
+        <v>552948</v>
       </c>
       <c r="R20" t="n">
-        <v>6469775</v>
+        <v>6469713</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,37 +2730,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344677</v>
+        <v>131344668</v>
       </c>
       <c r="B21" t="n">
-        <v>106159</v>
+        <v>99034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552948</v>
+        <v>552947</v>
       </c>
       <c r="R21" t="n">
-        <v>6469713</v>
+        <v>6469715</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131344668</v>
+        <v>131344651</v>
       </c>
       <c r="B22" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552947</v>
+        <v>552908</v>
       </c>
       <c r="R22" t="n">
-        <v>6469715</v>
+        <v>6469775</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131344683</v>
+        <v>131344648</v>
       </c>
       <c r="B23" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552914</v>
+        <v>552878</v>
       </c>
       <c r="R23" t="n">
-        <v>6469649</v>
+        <v>6469766</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131344687</v>
+        <v>131344683</v>
       </c>
       <c r="B24" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552921</v>
+        <v>552914</v>
       </c>
       <c r="R24" t="n">
-        <v>6469661</v>
+        <v>6469649</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3154,10 +3154,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131344648</v>
+        <v>131344687</v>
       </c>
       <c r="B25" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552878</v>
+        <v>552921</v>
       </c>
       <c r="R25" t="n">
-        <v>6469766</v>
+        <v>6469661</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131344658</v>
+        <v>131344663</v>
       </c>
       <c r="B26" t="n">
-        <v>57895</v>
+        <v>91849</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3293,13 +3293,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3307,10 +3306,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>553131</v>
+        <v>553051</v>
       </c>
       <c r="R26" t="n">
-        <v>6469899</v>
+        <v>6469833</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3345,17 +3344,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3374,10 +3369,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131344663</v>
+        <v>131344658</v>
       </c>
       <c r="B27" t="n">
-        <v>91849</v>
+        <v>57895</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3385,21 +3380,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3407,12 +3402,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3420,10 +3416,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>553051</v>
+        <v>553131</v>
       </c>
       <c r="R27" t="n">
-        <v>6469833</v>
+        <v>6469899</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3458,13 +3454,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>131344650</v>
       </c>
       <c r="B28" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131344670</v>
+        <v>131344660</v>
       </c>
       <c r="B29" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>552953</v>
+        <v>553080</v>
       </c>
       <c r="R29" t="n">
-        <v>6469707</v>
+        <v>6469846</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3695,10 +3695,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131344660</v>
+        <v>131344670</v>
       </c>
       <c r="B30" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>553080</v>
+        <v>552953</v>
       </c>
       <c r="R30" t="n">
-        <v>6469846</v>
+        <v>6469707</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131344674</v>
+        <v>131344666</v>
       </c>
       <c r="B32" t="n">
         <v>57895</v>
@@ -3943,11 +3943,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
@@ -3962,10 +3958,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552930</v>
+        <v>553049</v>
       </c>
       <c r="R32" t="n">
-        <v>6469714</v>
+        <v>6469673</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4029,7 +4025,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131344666</v>
+        <v>131344674</v>
       </c>
       <c r="B33" t="n">
         <v>57895</v>
@@ -4057,7 +4053,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>553049</v>
+        <v>552930</v>
       </c>
       <c r="R33" t="n">
-        <v>6469673</v>
+        <v>6469714</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4142,7 +4142,7 @@
         <v>131344704</v>
       </c>
       <c r="B34" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>131344646</v>
       </c>
       <c r="B35" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>131344680</v>
       </c>
       <c r="B36" t="n">
-        <v>101237</v>
+        <v>101238</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>131344691</v>
       </c>
       <c r="B37" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>131344659</v>
       </c>
       <c r="B39" t="n">
-        <v>97898</v>
+        <v>97899</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4773,42 +4773,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131344645</v>
+        <v>131344662</v>
       </c>
       <c r="B40" t="n">
-        <v>99033</v>
+        <v>91849</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4816,10 +4819,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552818</v>
+        <v>553053</v>
       </c>
       <c r="R40" t="n">
-        <v>6469702</v>
+        <v>6469836</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4993,45 +4996,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131344662</v>
+        <v>131344645</v>
       </c>
       <c r="B42" t="n">
-        <v>91849</v>
+        <v>99034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>553053</v>
+        <v>552818</v>
       </c>
       <c r="R42" t="n">
-        <v>6469836</v>
+        <v>6469702</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5105,7 +5105,7 @@
         <v>131344656</v>
       </c>
       <c r="B43" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5431,37 +5431,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131344669</v>
+        <v>131344657</v>
       </c>
       <c r="B46" t="n">
-        <v>99033</v>
+        <v>101238</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552952</v>
+        <v>552998</v>
       </c>
       <c r="R46" t="n">
-        <v>6469713</v>
+        <v>6469788</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5537,10 +5537,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131344685</v>
+        <v>131344669</v>
       </c>
       <c r="B47" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5580,10 +5580,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552922</v>
+        <v>552952</v>
       </c>
       <c r="R47" t="n">
-        <v>6469668</v>
+        <v>6469713</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131344675</v>
+        <v>131344685</v>
       </c>
       <c r="B48" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -5686,10 +5686,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552941</v>
+        <v>552922</v>
       </c>
       <c r="R48" t="n">
-        <v>6469708</v>
+        <v>6469668</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5749,10 +5749,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131344667</v>
+        <v>131344675</v>
       </c>
       <c r="B49" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552956</v>
+        <v>552941</v>
       </c>
       <c r="R49" t="n">
-        <v>6469709</v>
+        <v>6469708</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5855,37 +5855,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344657</v>
+        <v>131344667</v>
       </c>
       <c r="B50" t="n">
-        <v>101237</v>
+        <v>99034</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -5898,10 +5898,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552998</v>
+        <v>552956</v>
       </c>
       <c r="R50" t="n">
-        <v>6469788</v>
+        <v>6469709</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -792,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131344703</v>
+        <v>131344692</v>
       </c>
       <c r="B3" t="n">
-        <v>99034</v>
+        <v>79880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,7 +827,6 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552843</v>
+        <v>552907</v>
       </c>
       <c r="R3" t="n">
-        <v>6469679</v>
+        <v>6469684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131344676</v>
+        <v>131344703</v>
       </c>
       <c r="B4" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -941,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552946</v>
+        <v>552843</v>
       </c>
       <c r="R4" t="n">
-        <v>6469707</v>
+        <v>6469679</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131344688</v>
+        <v>131344676</v>
       </c>
       <c r="B5" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,7 +1033,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1047,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552928</v>
+        <v>552946</v>
       </c>
       <c r="R5" t="n">
-        <v>6469662</v>
+        <v>6469707</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131344684</v>
+        <v>131344688</v>
       </c>
       <c r="B6" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,7 +1139,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1153,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552919</v>
+        <v>552928</v>
       </c>
       <c r="R6" t="n">
-        <v>6469667</v>
+        <v>6469662</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,41 +1215,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131344692</v>
+        <v>131344684</v>
       </c>
       <c r="B7" t="n">
-        <v>79879</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552907</v>
+        <v>552919</v>
       </c>
       <c r="R7" t="n">
-        <v>6469684</v>
+        <v>6469667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1324,7 @@
         <v>131344679</v>
       </c>
       <c r="B8" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>131344678</v>
       </c>
       <c r="B9" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>131344654</v>
       </c>
       <c r="B10" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>131344696</v>
       </c>
       <c r="B11" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>131344698</v>
       </c>
       <c r="B12" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344647</v>
+        <v>131344689</v>
       </c>
       <c r="B13" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552884</v>
+        <v>552921</v>
       </c>
       <c r="R13" t="n">
-        <v>6469766</v>
+        <v>6469663</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,37 +1978,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344707</v>
+        <v>131344647</v>
       </c>
       <c r="B14" t="n">
-        <v>101238</v>
+        <v>99035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552818</v>
+        <v>552884</v>
       </c>
       <c r="R14" t="n">
-        <v>6469626</v>
+        <v>6469766</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344689</v>
+        <v>131344649</v>
       </c>
       <c r="B15" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552921</v>
+        <v>552893</v>
       </c>
       <c r="R15" t="n">
-        <v>6469663</v>
+        <v>6469762</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,37 +2190,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344649</v>
+        <v>131344707</v>
       </c>
       <c r="B16" t="n">
-        <v>99034</v>
+        <v>101239</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552893</v>
+        <v>552818</v>
       </c>
       <c r="R16" t="n">
-        <v>6469762</v>
+        <v>6469626</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,41 +2296,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131344686</v>
+        <v>131344677</v>
       </c>
       <c r="B17" t="n">
-        <v>79879</v>
+        <v>106161</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2338,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552925</v>
+        <v>552948</v>
       </c>
       <c r="R17" t="n">
-        <v>6469645</v>
+        <v>6469713</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,45 +2402,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344652</v>
+        <v>131344651</v>
       </c>
       <c r="B18" t="n">
-        <v>91849</v>
+        <v>99035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2447,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552916</v>
+        <v>552908</v>
       </c>
       <c r="R18" t="n">
-        <v>6469751</v>
+        <v>6469775</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2510,46 +2508,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344682</v>
+        <v>131344668</v>
       </c>
       <c r="B19" t="n">
-        <v>57895</v>
+        <v>99035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2557,10 +2551,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552956</v>
+        <v>552947</v>
       </c>
       <c r="R19" t="n">
-        <v>6469666</v>
+        <v>6469715</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,17 +2589,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2624,42 +2614,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344677</v>
+        <v>131344686</v>
       </c>
       <c r="B20" t="n">
-        <v>106160</v>
+        <v>79880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2667,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552948</v>
+        <v>552925</v>
       </c>
       <c r="R20" t="n">
-        <v>6469713</v>
+        <v>6469645</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,42 +2719,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344668</v>
+        <v>131344652</v>
       </c>
       <c r="B21" t="n">
-        <v>99034</v>
+        <v>91850</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2773,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552947</v>
+        <v>552916</v>
       </c>
       <c r="R21" t="n">
-        <v>6469715</v>
+        <v>6469751</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,42 +2828,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131344651</v>
+        <v>131344682</v>
       </c>
       <c r="B22" t="n">
-        <v>99034</v>
+        <v>57896</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2879,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552908</v>
+        <v>552956</v>
       </c>
       <c r="R22" t="n">
-        <v>6469775</v>
+        <v>6469666</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2917,13 +2913,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131344648</v>
+        <v>131344683</v>
       </c>
       <c r="B23" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552878</v>
+        <v>552914</v>
       </c>
       <c r="R23" t="n">
-        <v>6469766</v>
+        <v>6469649</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131344683</v>
+        <v>131344687</v>
       </c>
       <c r="B24" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552914</v>
+        <v>552921</v>
       </c>
       <c r="R24" t="n">
-        <v>6469649</v>
+        <v>6469661</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3154,10 +3154,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131344687</v>
+        <v>131344648</v>
       </c>
       <c r="B25" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552921</v>
+        <v>552878</v>
       </c>
       <c r="R25" t="n">
-        <v>6469661</v>
+        <v>6469766</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3260,45 +3260,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131344663</v>
+        <v>131344650</v>
       </c>
       <c r="B26" t="n">
-        <v>91849</v>
+        <v>99035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3306,10 +3303,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>553051</v>
+        <v>552899</v>
       </c>
       <c r="R26" t="n">
-        <v>6469833</v>
+        <v>6469774</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3372,7 +3369,7 @@
         <v>131344658</v>
       </c>
       <c r="B27" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3483,42 +3480,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131344650</v>
+        <v>131344663</v>
       </c>
       <c r="B28" t="n">
-        <v>99034</v>
+        <v>91850</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>552899</v>
+        <v>553051</v>
       </c>
       <c r="R28" t="n">
-        <v>6469774</v>
+        <v>6469833</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131344660</v>
+        <v>131344670</v>
       </c>
       <c r="B29" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>553080</v>
+        <v>552953</v>
       </c>
       <c r="R29" t="n">
-        <v>6469846</v>
+        <v>6469707</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3695,10 +3695,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131344670</v>
+        <v>131344660</v>
       </c>
       <c r="B30" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>552953</v>
+        <v>553080</v>
       </c>
       <c r="R30" t="n">
-        <v>6469707</v>
+        <v>6469846</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3804,7 +3804,7 @@
         <v>131344653</v>
       </c>
       <c r="B31" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3915,10 +3915,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131344666</v>
+        <v>131344674</v>
       </c>
       <c r="B32" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3943,7 +3943,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
@@ -3958,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>553049</v>
+        <v>552930</v>
       </c>
       <c r="R32" t="n">
-        <v>6469673</v>
+        <v>6469714</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4025,10 +4029,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131344674</v>
+        <v>131344666</v>
       </c>
       <c r="B33" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4053,11 +4057,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552930</v>
+        <v>553049</v>
       </c>
       <c r="R33" t="n">
-        <v>6469714</v>
+        <v>6469673</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4142,7 +4142,7 @@
         <v>131344704</v>
       </c>
       <c r="B34" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>131344646</v>
       </c>
       <c r="B35" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>131344680</v>
       </c>
       <c r="B36" t="n">
-        <v>101238</v>
+        <v>101239</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>131344691</v>
       </c>
       <c r="B37" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4563,56 +4563,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131344661</v>
+        <v>131344659</v>
       </c>
       <c r="B38" t="n">
-        <v>91849</v>
+        <v>97900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>553051</v>
+        <v>553082</v>
       </c>
       <c r="R38" t="n">
-        <v>6469846</v>
+        <v>6469843</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4653,7 +4646,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4672,49 +4664,56 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131344659</v>
+        <v>131344661</v>
       </c>
       <c r="B39" t="n">
-        <v>97899</v>
+        <v>91850</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>553082</v>
+        <v>553051</v>
       </c>
       <c r="R39" t="n">
-        <v>6469843</v>
+        <v>6469846</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4755,6 +4754,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4773,45 +4773,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131344662</v>
+        <v>131344645</v>
       </c>
       <c r="B40" t="n">
-        <v>91849</v>
+        <v>99035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4819,10 +4816,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>553053</v>
+        <v>552818</v>
       </c>
       <c r="R40" t="n">
-        <v>6469836</v>
+        <v>6469702</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4882,10 +4879,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131344705</v>
+        <v>131344662</v>
       </c>
       <c r="B41" t="n">
-        <v>57895</v>
+        <v>91850</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4893,21 +4890,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4915,13 +4912,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4929,10 +4925,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>552781</v>
+        <v>553053</v>
       </c>
       <c r="R41" t="n">
-        <v>6469669</v>
+        <v>6469836</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4967,17 +4963,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4996,42 +4988,46 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131344645</v>
+        <v>131344705</v>
       </c>
       <c r="B42" t="n">
-        <v>99034</v>
+        <v>57896</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5039,10 +5035,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>552818</v>
+        <v>552781</v>
       </c>
       <c r="R42" t="n">
-        <v>6469702</v>
+        <v>6469669</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5077,13 +5073,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>131344656</v>
       </c>
       <c r="B43" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5208,46 +5208,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131344706</v>
+        <v>131344669</v>
       </c>
       <c r="B44" t="n">
-        <v>57895</v>
+        <v>99035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5255,10 +5251,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552813</v>
+        <v>552952</v>
       </c>
       <c r="R44" t="n">
-        <v>6469628</v>
+        <v>6469713</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5293,17 +5289,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5322,46 +5314,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131344673</v>
+        <v>131344685</v>
       </c>
       <c r="B45" t="n">
-        <v>58055</v>
+        <v>99035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5369,10 +5357,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552942</v>
+        <v>552922</v>
       </c>
       <c r="R45" t="n">
-        <v>6469709</v>
+        <v>6469668</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,6 +5401,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5431,37 +5420,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131344657</v>
+        <v>131344675</v>
       </c>
       <c r="B46" t="n">
-        <v>101238</v>
+        <v>99035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5474,10 +5463,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552998</v>
+        <v>552941</v>
       </c>
       <c r="R46" t="n">
-        <v>6469788</v>
+        <v>6469708</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5537,10 +5526,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131344669</v>
+        <v>131344667</v>
       </c>
       <c r="B47" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5567,7 +5556,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5580,10 +5569,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552952</v>
+        <v>552956</v>
       </c>
       <c r="R47" t="n">
-        <v>6469713</v>
+        <v>6469709</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5643,42 +5632,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131344685</v>
+        <v>131344706</v>
       </c>
       <c r="B48" t="n">
-        <v>99034</v>
+        <v>57896</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5686,10 +5679,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552922</v>
+        <v>552813</v>
       </c>
       <c r="R48" t="n">
-        <v>6469668</v>
+        <v>6469628</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5724,13 +5717,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5749,42 +5746,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131344675</v>
+        <v>131344673</v>
       </c>
       <c r="B49" t="n">
-        <v>99034</v>
+        <v>58056</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5792,10 +5793,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552941</v>
+        <v>552942</v>
       </c>
       <c r="R49" t="n">
-        <v>6469708</v>
+        <v>6469709</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5836,7 +5837,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5855,37 +5855,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344667</v>
+        <v>131344657</v>
       </c>
       <c r="B50" t="n">
-        <v>99034</v>
+        <v>101239</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -5898,10 +5898,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552956</v>
+        <v>552998</v>
       </c>
       <c r="R50" t="n">
-        <v>6469709</v>
+        <v>6469788</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5964,7 +5964,7 @@
         <v>131344655</v>
       </c>
       <c r="B51" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131344692</v>
       </c>
       <c r="B3" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>131344703</v>
       </c>
       <c r="B4" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>131344676</v>
       </c>
       <c r="B5" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>131344688</v>
       </c>
       <c r="B6" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>131344684</v>
       </c>
       <c r="B7" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>131344679</v>
       </c>
       <c r="B8" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>131344678</v>
       </c>
       <c r="B9" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>131344654</v>
       </c>
       <c r="B10" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>131344696</v>
       </c>
       <c r="B11" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,41 +1767,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131344698</v>
+        <v>131344647</v>
       </c>
       <c r="B12" t="n">
-        <v>79880</v>
+        <v>99038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1809,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552887</v>
+        <v>552884</v>
       </c>
       <c r="R12" t="n">
-        <v>6469694</v>
+        <v>6469766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344689</v>
+        <v>131344649</v>
       </c>
       <c r="B13" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1903,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1915,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552921</v>
+        <v>552893</v>
       </c>
       <c r="R13" t="n">
-        <v>6469663</v>
+        <v>6469762</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344647</v>
+        <v>131344689</v>
       </c>
       <c r="B14" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2009,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2021,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552884</v>
+        <v>552921</v>
       </c>
       <c r="R14" t="n">
-        <v>6469766</v>
+        <v>6469663</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,42 +2085,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344649</v>
+        <v>131344698</v>
       </c>
       <c r="B15" t="n">
-        <v>99035</v>
+        <v>79883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552893</v>
+        <v>552887</v>
       </c>
       <c r="R15" t="n">
-        <v>6469762</v>
+        <v>6469694</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,7 +2193,7 @@
         <v>131344707</v>
       </c>
       <c r="B16" t="n">
-        <v>101239</v>
+        <v>101242</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,42 +2296,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131344677</v>
+        <v>131344686</v>
       </c>
       <c r="B17" t="n">
-        <v>106161</v>
+        <v>79883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2339,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552948</v>
+        <v>552925</v>
       </c>
       <c r="R17" t="n">
-        <v>6469713</v>
+        <v>6469645</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,42 +2401,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344651</v>
+        <v>131344652</v>
       </c>
       <c r="B18" t="n">
-        <v>99035</v>
+        <v>91853</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2445,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552908</v>
+        <v>552916</v>
       </c>
       <c r="R18" t="n">
-        <v>6469775</v>
+        <v>6469751</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,42 +2510,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344668</v>
+        <v>131344682</v>
       </c>
       <c r="B19" t="n">
-        <v>99035</v>
+        <v>57899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2551,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552947</v>
+        <v>552956</v>
       </c>
       <c r="R19" t="n">
-        <v>6469715</v>
+        <v>6469666</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,13 +2595,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2614,41 +2624,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344686</v>
+        <v>131344668</v>
       </c>
       <c r="B20" t="n">
-        <v>79880</v>
+        <v>99038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2656,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552925</v>
+        <v>552947</v>
       </c>
       <c r="R20" t="n">
-        <v>6469645</v>
+        <v>6469715</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2719,45 +2730,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344652</v>
+        <v>131344651</v>
       </c>
       <c r="B21" t="n">
-        <v>91850</v>
+        <v>99038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2765,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552916</v>
+        <v>552908</v>
       </c>
       <c r="R21" t="n">
-        <v>6469751</v>
+        <v>6469775</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,46 +2836,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131344682</v>
+        <v>131344677</v>
       </c>
       <c r="B22" t="n">
-        <v>57896</v>
+        <v>106159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2875,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552956</v>
+        <v>552948</v>
       </c>
       <c r="R22" t="n">
-        <v>6469666</v>
+        <v>6469713</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,17 +2917,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>131344683</v>
       </c>
       <c r="B23" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>131344687</v>
       </c>
       <c r="B24" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>131344648</v>
       </c>
       <c r="B25" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,42 +3260,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131344650</v>
+        <v>131344658</v>
       </c>
       <c r="B26" t="n">
-        <v>99035</v>
+        <v>57899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3303,10 +3307,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552899</v>
+        <v>553131</v>
       </c>
       <c r="R26" t="n">
-        <v>6469774</v>
+        <v>6469899</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3341,13 +3345,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3366,10 +3374,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131344658</v>
+        <v>131344663</v>
       </c>
       <c r="B27" t="n">
-        <v>57896</v>
+        <v>91853</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,21 +3385,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3399,13 +3407,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3413,10 +3420,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>553131</v>
+        <v>553051</v>
       </c>
       <c r="R27" t="n">
-        <v>6469899</v>
+        <v>6469833</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3451,17 +3458,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3480,45 +3483,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131344663</v>
+        <v>131344650</v>
       </c>
       <c r="B28" t="n">
-        <v>91850</v>
+        <v>99038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>553051</v>
+        <v>552899</v>
       </c>
       <c r="R28" t="n">
-        <v>6469833</v>
+        <v>6469774</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3592,7 +3592,7 @@
         <v>131344670</v>
       </c>
       <c r="B29" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>131344660</v>
       </c>
       <c r="B30" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>131344653</v>
       </c>
       <c r="B31" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>131344674</v>
       </c>
       <c r="B32" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>131344666</v>
       </c>
       <c r="B33" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>131344704</v>
       </c>
       <c r="B34" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>131344646</v>
       </c>
       <c r="B35" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>131344680</v>
       </c>
       <c r="B36" t="n">
-        <v>101239</v>
+        <v>101242</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>131344691</v>
       </c>
       <c r="B37" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4563,49 +4563,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131344659</v>
+        <v>131344661</v>
       </c>
       <c r="B38" t="n">
-        <v>97900</v>
+        <v>91853</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>553082</v>
+        <v>553051</v>
       </c>
       <c r="R38" t="n">
-        <v>6469843</v>
+        <v>6469846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4646,6 +4653,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4664,56 +4672,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131344661</v>
+        <v>131344659</v>
       </c>
       <c r="B39" t="n">
-        <v>91850</v>
+        <v>97903</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>553051</v>
+        <v>553082</v>
       </c>
       <c r="R39" t="n">
-        <v>6469846</v>
+        <v>6469843</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4754,7 +4755,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4773,42 +4773,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131344645</v>
+        <v>131344662</v>
       </c>
       <c r="B40" t="n">
-        <v>99035</v>
+        <v>91853</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4816,10 +4819,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552818</v>
+        <v>553053</v>
       </c>
       <c r="R40" t="n">
-        <v>6469702</v>
+        <v>6469836</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4879,10 +4882,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131344662</v>
+        <v>131344705</v>
       </c>
       <c r="B41" t="n">
-        <v>91850</v>
+        <v>57899</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,21 +4893,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4912,12 +4915,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4925,10 +4929,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>553053</v>
+        <v>552781</v>
       </c>
       <c r="R41" t="n">
-        <v>6469836</v>
+        <v>6469669</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4963,13 +4967,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4988,46 +4996,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131344705</v>
+        <v>131344645</v>
       </c>
       <c r="B42" t="n">
-        <v>57896</v>
+        <v>99038</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5035,10 +5039,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>552781</v>
+        <v>552818</v>
       </c>
       <c r="R42" t="n">
-        <v>6469669</v>
+        <v>6469702</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,17 +5077,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>131344656</v>
       </c>
       <c r="B43" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>131344669</v>
       </c>
       <c r="B44" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5314,10 +5314,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131344685</v>
+        <v>131344675</v>
       </c>
       <c r="B45" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552922</v>
+        <v>552941</v>
       </c>
       <c r="R45" t="n">
-        <v>6469668</v>
+        <v>6469708</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5420,10 +5420,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131344675</v>
+        <v>131344667</v>
       </c>
       <c r="B46" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552941</v>
+        <v>552956</v>
       </c>
       <c r="R46" t="n">
-        <v>6469708</v>
+        <v>6469709</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5526,10 +5526,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131344667</v>
+        <v>131344685</v>
       </c>
       <c r="B47" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552956</v>
+        <v>552922</v>
       </c>
       <c r="R47" t="n">
-        <v>6469709</v>
+        <v>6469668</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5632,46 +5632,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131344706</v>
+        <v>131344657</v>
       </c>
       <c r="B48" t="n">
-        <v>57896</v>
+        <v>101242</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5679,10 +5675,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552813</v>
+        <v>552998</v>
       </c>
       <c r="R48" t="n">
-        <v>6469628</v>
+        <v>6469788</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5717,17 +5713,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5749,7 +5741,7 @@
         <v>131344673</v>
       </c>
       <c r="B49" t="n">
-        <v>58056</v>
+        <v>58059</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5855,42 +5847,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344657</v>
+        <v>131344706</v>
       </c>
       <c r="B50" t="n">
-        <v>101239</v>
+        <v>57899</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5898,10 +5894,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552998</v>
+        <v>552813</v>
       </c>
       <c r="R50" t="n">
-        <v>6469788</v>
+        <v>6469628</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5936,13 +5932,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5964,7 +5964,7 @@
         <v>131344655</v>
       </c>
       <c r="B51" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131344703</v>
+        <v>131344688</v>
       </c>
       <c r="B4" t="n">
         <v>99038</v>
@@ -927,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552843</v>
+        <v>552928</v>
       </c>
       <c r="R4" t="n">
-        <v>6469679</v>
+        <v>6469662</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131344676</v>
+        <v>131344684</v>
       </c>
       <c r="B5" t="n">
         <v>99038</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552946</v>
+        <v>552919</v>
       </c>
       <c r="R5" t="n">
-        <v>6469707</v>
+        <v>6469667</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131344688</v>
+        <v>131344703</v>
       </c>
       <c r="B6" t="n">
         <v>99038</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552928</v>
+        <v>552843</v>
       </c>
       <c r="R6" t="n">
-        <v>6469662</v>
+        <v>6469679</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131344684</v>
+        <v>131344676</v>
       </c>
       <c r="B7" t="n">
         <v>99038</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552919</v>
+        <v>552946</v>
       </c>
       <c r="R7" t="n">
-        <v>6469667</v>
+        <v>6469707</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131344678</v>
+        <v>131344654</v>
       </c>
       <c r="B9" t="n">
-        <v>91853</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1441,34 +1441,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1476,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552948</v>
+        <v>552967</v>
       </c>
       <c r="R9" t="n">
-        <v>6469706</v>
+        <v>6469782</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,13 +1515,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1539,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131344654</v>
+        <v>131344678</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>91853</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,35 +1555,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1586,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552967</v>
+        <v>552948</v>
       </c>
       <c r="R10" t="n">
-        <v>6469782</v>
+        <v>6469706</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,17 +1628,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1767,7 +1767,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131344647</v>
+        <v>131344689</v>
       </c>
       <c r="B12" t="n">
         <v>99038</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552884</v>
+        <v>552921</v>
       </c>
       <c r="R12" t="n">
-        <v>6469766</v>
+        <v>6469663</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,7 +1873,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344649</v>
+        <v>131344647</v>
       </c>
       <c r="B13" t="n">
         <v>99038</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552893</v>
+        <v>552884</v>
       </c>
       <c r="R13" t="n">
-        <v>6469762</v>
+        <v>6469766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,7 +1979,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344689</v>
+        <v>131344649</v>
       </c>
       <c r="B14" t="n">
         <v>99038</v>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552921</v>
+        <v>552893</v>
       </c>
       <c r="R14" t="n">
-        <v>6469663</v>
+        <v>6469762</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2193,7 +2193,7 @@
         <v>131344707</v>
       </c>
       <c r="B16" t="n">
-        <v>101242</v>
+        <v>101243</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344668</v>
+        <v>131344651</v>
       </c>
       <c r="B20" t="n">
         <v>99038</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552947</v>
+        <v>552908</v>
       </c>
       <c r="R20" t="n">
-        <v>6469715</v>
+        <v>6469775</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,37 +2730,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344651</v>
+        <v>131344677</v>
       </c>
       <c r="B21" t="n">
-        <v>99038</v>
+        <v>106160</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552908</v>
+        <v>552948</v>
       </c>
       <c r="R21" t="n">
-        <v>6469775</v>
+        <v>6469713</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,37 +2836,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131344677</v>
+        <v>131344668</v>
       </c>
       <c r="B22" t="n">
-        <v>106159</v>
+        <v>99038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552948</v>
+        <v>552947</v>
       </c>
       <c r="R22" t="n">
-        <v>6469713</v>
+        <v>6469715</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3589,7 +3589,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131344670</v>
+        <v>131344660</v>
       </c>
       <c r="B29" t="n">
         <v>99038</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>552953</v>
+        <v>553080</v>
       </c>
       <c r="R29" t="n">
-        <v>6469707</v>
+        <v>6469846</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3695,7 +3695,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131344660</v>
+        <v>131344670</v>
       </c>
       <c r="B30" t="n">
         <v>99038</v>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>553080</v>
+        <v>552953</v>
       </c>
       <c r="R30" t="n">
-        <v>6469846</v>
+        <v>6469707</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3915,46 +3915,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131344674</v>
+        <v>131344704</v>
       </c>
       <c r="B32" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3962,10 +3958,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552930</v>
+        <v>552824</v>
       </c>
       <c r="R32" t="n">
-        <v>6469714</v>
+        <v>6469659</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4000,17 +3996,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4029,42 +4021,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131344666</v>
+        <v>131344646</v>
       </c>
       <c r="B33" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4072,10 +4064,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>553049</v>
+        <v>552813</v>
       </c>
       <c r="R33" t="n">
-        <v>6469673</v>
+        <v>6469703</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4110,17 +4102,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4139,42 +4127,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131344704</v>
+        <v>131344674</v>
       </c>
       <c r="B34" t="n">
-        <v>99038</v>
+        <v>57899</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4182,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552824</v>
+        <v>552930</v>
       </c>
       <c r="R34" t="n">
-        <v>6469659</v>
+        <v>6469714</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4220,13 +4212,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4245,42 +4241,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131344646</v>
+        <v>131344666</v>
       </c>
       <c r="B35" t="n">
-        <v>99038</v>
+        <v>57899</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4288,10 +4284,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552813</v>
+        <v>553049</v>
       </c>
       <c r="R35" t="n">
-        <v>6469703</v>
+        <v>6469673</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4326,13 +4322,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>131344680</v>
       </c>
       <c r="B36" t="n">
-        <v>101242</v>
+        <v>101243</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,56 +4563,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131344661</v>
+        <v>131344659</v>
       </c>
       <c r="B38" t="n">
-        <v>91853</v>
+        <v>97903</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>553051</v>
+        <v>553082</v>
       </c>
       <c r="R38" t="n">
-        <v>6469846</v>
+        <v>6469843</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4653,7 +4646,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4672,49 +4664,56 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131344659</v>
+        <v>131344661</v>
       </c>
       <c r="B39" t="n">
-        <v>97903</v>
+        <v>91853</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>553082</v>
+        <v>553051</v>
       </c>
       <c r="R39" t="n">
-        <v>6469843</v>
+        <v>6469846</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4755,6 +4754,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5208,42 +5208,46 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131344669</v>
+        <v>131344706</v>
       </c>
       <c r="B44" t="n">
-        <v>99038</v>
+        <v>57899</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5251,10 +5255,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552952</v>
+        <v>552813</v>
       </c>
       <c r="R44" t="n">
-        <v>6469713</v>
+        <v>6469628</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5289,13 +5293,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5314,42 +5322,46 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131344675</v>
+        <v>131344673</v>
       </c>
       <c r="B45" t="n">
-        <v>99038</v>
+        <v>58059</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5357,10 +5369,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552941</v>
+        <v>552942</v>
       </c>
       <c r="R45" t="n">
-        <v>6469708</v>
+        <v>6469709</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5401,7 +5413,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5420,7 +5431,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131344667</v>
+        <v>131344669</v>
       </c>
       <c r="B46" t="n">
         <v>99038</v>
@@ -5450,7 +5461,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5463,10 +5474,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552956</v>
+        <v>552952</v>
       </c>
       <c r="R46" t="n">
-        <v>6469709</v>
+        <v>6469713</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5526,7 +5537,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131344685</v>
+        <v>131344667</v>
       </c>
       <c r="B47" t="n">
         <v>99038</v>
@@ -5556,7 +5567,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5569,10 +5580,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552922</v>
+        <v>552956</v>
       </c>
       <c r="R47" t="n">
-        <v>6469668</v>
+        <v>6469709</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5635,7 +5646,7 @@
         <v>131344657</v>
       </c>
       <c r="B48" t="n">
-        <v>101242</v>
+        <v>101243</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5738,46 +5749,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131344673</v>
+        <v>131344685</v>
       </c>
       <c r="B49" t="n">
-        <v>58059</v>
+        <v>99038</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5785,10 +5792,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552942</v>
+        <v>552922</v>
       </c>
       <c r="R49" t="n">
-        <v>6469709</v>
+        <v>6469668</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5829,6 +5836,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5847,46 +5855,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344706</v>
+        <v>131344675</v>
       </c>
       <c r="B50" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5894,10 +5898,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552813</v>
+        <v>552941</v>
       </c>
       <c r="R50" t="n">
-        <v>6469628</v>
+        <v>6469708</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5932,17 +5936,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131344688</v>
+        <v>131344703</v>
       </c>
       <c r="B4" t="n">
         <v>99038</v>
@@ -927,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552928</v>
+        <v>552843</v>
       </c>
       <c r="R4" t="n">
-        <v>6469662</v>
+        <v>6469679</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131344684</v>
+        <v>131344676</v>
       </c>
       <c r="B5" t="n">
         <v>99038</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552919</v>
+        <v>552946</v>
       </c>
       <c r="R5" t="n">
-        <v>6469667</v>
+        <v>6469707</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131344703</v>
+        <v>131344688</v>
       </c>
       <c r="B6" t="n">
         <v>99038</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552843</v>
+        <v>552928</v>
       </c>
       <c r="R6" t="n">
-        <v>6469679</v>
+        <v>6469662</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131344676</v>
+        <v>131344684</v>
       </c>
       <c r="B7" t="n">
         <v>99038</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552946</v>
+        <v>552919</v>
       </c>
       <c r="R7" t="n">
-        <v>6469707</v>
+        <v>6469667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131344654</v>
+        <v>131344678</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>91853</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1441,35 +1441,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1477,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552967</v>
+        <v>552948</v>
       </c>
       <c r="R9" t="n">
-        <v>6469782</v>
+        <v>6469706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,17 +1514,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1544,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131344678</v>
+        <v>131344654</v>
       </c>
       <c r="B10" t="n">
-        <v>91853</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,34 +1550,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1590,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552948</v>
+        <v>552967</v>
       </c>
       <c r="R10" t="n">
-        <v>6469706</v>
+        <v>6469782</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,13 +1624,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1767,42 +1767,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131344689</v>
+        <v>131344698</v>
       </c>
       <c r="B12" t="n">
-        <v>99038</v>
+        <v>79883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1810,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552921</v>
+        <v>552887</v>
       </c>
       <c r="R12" t="n">
-        <v>6469663</v>
+        <v>6469694</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,7 +1872,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344647</v>
+        <v>131344689</v>
       </c>
       <c r="B13" t="n">
         <v>99038</v>
@@ -1903,7 +1902,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1916,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552884</v>
+        <v>552921</v>
       </c>
       <c r="R13" t="n">
-        <v>6469766</v>
+        <v>6469663</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,7 +1978,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344649</v>
+        <v>131344647</v>
       </c>
       <c r="B14" t="n">
         <v>99038</v>
@@ -2009,7 +2008,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2022,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552893</v>
+        <v>552884</v>
       </c>
       <c r="R14" t="n">
-        <v>6469762</v>
+        <v>6469766</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,41 +2084,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344698</v>
+        <v>131344649</v>
       </c>
       <c r="B15" t="n">
-        <v>79883</v>
+        <v>99038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552887</v>
+        <v>552893</v>
       </c>
       <c r="R15" t="n">
-        <v>6469694</v>
+        <v>6469762</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2289,48 +2289,49 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131344686</v>
+        <v>131344651</v>
       </c>
       <c r="B17" t="n">
-        <v>79883</v>
+        <v>99038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2338,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552925</v>
+        <v>552908</v>
       </c>
       <c r="R17" t="n">
-        <v>6469645</v>
+        <v>6469775</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,45 +2402,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344652</v>
+        <v>131344677</v>
       </c>
       <c r="B18" t="n">
-        <v>91853</v>
+        <v>106160</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2447,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552916</v>
+        <v>552948</v>
       </c>
       <c r="R18" t="n">
-        <v>6469751</v>
+        <v>6469713</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2510,46 +2508,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344682</v>
+        <v>131344668</v>
       </c>
       <c r="B19" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2557,10 +2551,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552956</v>
+        <v>552947</v>
       </c>
       <c r="R19" t="n">
-        <v>6469666</v>
+        <v>6469715</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,17 +2589,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2624,42 +2614,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344651</v>
+        <v>131344686</v>
       </c>
       <c r="B20" t="n">
-        <v>99038</v>
+        <v>79883</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2667,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552908</v>
+        <v>552925</v>
       </c>
       <c r="R20" t="n">
-        <v>6469775</v>
+        <v>6469645</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,42 +2719,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344677</v>
+        <v>131344652</v>
       </c>
       <c r="B21" t="n">
-        <v>106160</v>
+        <v>91853</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2773,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552948</v>
+        <v>552916</v>
       </c>
       <c r="R21" t="n">
-        <v>6469713</v>
+        <v>6469751</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,42 +2828,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131344668</v>
+        <v>131344682</v>
       </c>
       <c r="B22" t="n">
-        <v>99038</v>
+        <v>57899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2879,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552947</v>
+        <v>552956</v>
       </c>
       <c r="R22" t="n">
-        <v>6469715</v>
+        <v>6469666</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2917,13 +2913,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131344658</v>
+        <v>131344663</v>
       </c>
       <c r="B26" t="n">
-        <v>57899</v>
+        <v>91853</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3293,13 +3293,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3307,10 +3306,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>553131</v>
+        <v>553051</v>
       </c>
       <c r="R26" t="n">
-        <v>6469899</v>
+        <v>6469833</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3345,17 +3344,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3374,10 +3369,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131344663</v>
+        <v>131344658</v>
       </c>
       <c r="B27" t="n">
-        <v>91853</v>
+        <v>57899</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3385,21 +3380,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3407,12 +3402,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3420,10 +3416,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>553051</v>
+        <v>553131</v>
       </c>
       <c r="R27" t="n">
-        <v>6469833</v>
+        <v>6469899</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3458,13 +3454,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3589,7 +3589,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131344660</v>
+        <v>131344670</v>
       </c>
       <c r="B29" t="n">
         <v>99038</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>553080</v>
+        <v>552953</v>
       </c>
       <c r="R29" t="n">
-        <v>6469846</v>
+        <v>6469707</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3695,7 +3695,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131344670</v>
+        <v>131344660</v>
       </c>
       <c r="B30" t="n">
         <v>99038</v>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>552953</v>
+        <v>553080</v>
       </c>
       <c r="R30" t="n">
-        <v>6469707</v>
+        <v>6469846</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3915,42 +3915,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131344704</v>
+        <v>131344674</v>
       </c>
       <c r="B32" t="n">
-        <v>99038</v>
+        <v>57899</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3958,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552824</v>
+        <v>552930</v>
       </c>
       <c r="R32" t="n">
-        <v>6469659</v>
+        <v>6469714</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,13 +4000,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4021,42 +4029,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131344646</v>
+        <v>131344666</v>
       </c>
       <c r="B33" t="n">
-        <v>99038</v>
+        <v>57899</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4064,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552813</v>
+        <v>553049</v>
       </c>
       <c r="R33" t="n">
-        <v>6469703</v>
+        <v>6469673</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4102,13 +4110,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4127,46 +4139,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131344674</v>
+        <v>131344704</v>
       </c>
       <c r="B34" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4174,10 +4182,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552930</v>
+        <v>552824</v>
       </c>
       <c r="R34" t="n">
-        <v>6469714</v>
+        <v>6469659</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4212,17 +4220,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4234,49 +4238,49 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131344666</v>
+        <v>131344646</v>
       </c>
       <c r="B35" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4284,10 +4288,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>553049</v>
+        <v>552813</v>
       </c>
       <c r="R35" t="n">
-        <v>6469673</v>
+        <v>6469703</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4322,17 +4326,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4563,49 +4563,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131344659</v>
+        <v>131344661</v>
       </c>
       <c r="B38" t="n">
-        <v>97903</v>
+        <v>91853</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>553082</v>
+        <v>553051</v>
       </c>
       <c r="R38" t="n">
-        <v>6469843</v>
+        <v>6469846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4646,6 +4653,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4664,56 +4672,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131344661</v>
+        <v>131344659</v>
       </c>
       <c r="B39" t="n">
-        <v>91853</v>
+        <v>97903</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>553051</v>
+        <v>553082</v>
       </c>
       <c r="R39" t="n">
-        <v>6469846</v>
+        <v>6469843</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4754,7 +4755,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4773,10 +4773,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131344662</v>
+        <v>131344705</v>
       </c>
       <c r="B40" t="n">
-        <v>91853</v>
+        <v>57899</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4784,21 +4784,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4806,12 +4806,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4819,10 +4820,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>553053</v>
+        <v>552781</v>
       </c>
       <c r="R40" t="n">
-        <v>6469836</v>
+        <v>6469669</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4857,13 +4858,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4875,17 +4880,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131344705</v>
+        <v>131344662</v>
       </c>
       <c r="B41" t="n">
-        <v>57899</v>
+        <v>91853</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4893,21 +4898,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4915,13 +4920,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4929,10 +4933,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>552781</v>
+        <v>553053</v>
       </c>
       <c r="R41" t="n">
-        <v>6469669</v>
+        <v>6469836</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4967,17 +4971,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5315,53 +5315,49 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131344673</v>
+        <v>131344669</v>
       </c>
       <c r="B45" t="n">
-        <v>58059</v>
+        <v>99038</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5369,10 +5365,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552942</v>
+        <v>552952</v>
       </c>
       <c r="R45" t="n">
-        <v>6469709</v>
+        <v>6469713</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,6 +5409,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5431,7 +5428,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131344669</v>
+        <v>131344685</v>
       </c>
       <c r="B46" t="n">
         <v>99038</v>
@@ -5461,7 +5458,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5474,10 +5471,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552952</v>
+        <v>552922</v>
       </c>
       <c r="R46" t="n">
-        <v>6469713</v>
+        <v>6469668</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5537,7 +5534,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131344667</v>
+        <v>131344675</v>
       </c>
       <c r="B47" t="n">
         <v>99038</v>
@@ -5567,7 +5564,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5580,10 +5577,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552956</v>
+        <v>552941</v>
       </c>
       <c r="R47" t="n">
-        <v>6469709</v>
+        <v>6469708</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5643,37 +5640,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131344657</v>
+        <v>131344667</v>
       </c>
       <c r="B48" t="n">
-        <v>101243</v>
+        <v>99038</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -5686,10 +5683,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552998</v>
+        <v>552956</v>
       </c>
       <c r="R48" t="n">
-        <v>6469788</v>
+        <v>6469709</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5749,37 +5746,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131344685</v>
+        <v>131344657</v>
       </c>
       <c r="B49" t="n">
-        <v>99038</v>
+        <v>101243</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -5792,10 +5789,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552922</v>
+        <v>552998</v>
       </c>
       <c r="R49" t="n">
-        <v>6469668</v>
+        <v>6469788</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5855,42 +5852,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344675</v>
+        <v>131344673</v>
       </c>
       <c r="B50" t="n">
-        <v>99038</v>
+        <v>58059</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5898,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552941</v>
+        <v>552942</v>
       </c>
       <c r="R50" t="n">
-        <v>6469708</v>
+        <v>6469709</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5942,7 +5943,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -1767,41 +1767,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131344698</v>
+        <v>131344689</v>
       </c>
       <c r="B12" t="n">
-        <v>79883</v>
+        <v>99038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1809,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552887</v>
+        <v>552921</v>
       </c>
       <c r="R12" t="n">
-        <v>6469694</v>
+        <v>6469663</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,7 +1873,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344689</v>
+        <v>131344647</v>
       </c>
       <c r="B13" t="n">
         <v>99038</v>
@@ -1902,7 +1903,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1915,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552921</v>
+        <v>552884</v>
       </c>
       <c r="R13" t="n">
-        <v>6469663</v>
+        <v>6469766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,7 +1979,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344647</v>
+        <v>131344649</v>
       </c>
       <c r="B14" t="n">
         <v>99038</v>
@@ -2008,7 +2009,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2021,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552884</v>
+        <v>552893</v>
       </c>
       <c r="R14" t="n">
-        <v>6469766</v>
+        <v>6469762</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,42 +2085,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344649</v>
+        <v>131344698</v>
       </c>
       <c r="B15" t="n">
-        <v>99038</v>
+        <v>79883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552893</v>
+        <v>552887</v>
       </c>
       <c r="R15" t="n">
-        <v>6469762</v>
+        <v>6469694</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131344674</v>
+        <v>131344666</v>
       </c>
       <c r="B32" t="n">
         <v>57899</v>
@@ -3943,11 +3943,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
@@ -3962,10 +3958,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552930</v>
+        <v>553049</v>
       </c>
       <c r="R32" t="n">
-        <v>6469714</v>
+        <v>6469673</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4029,42 +4025,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131344666</v>
+        <v>131344704</v>
       </c>
       <c r="B33" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4072,10 +4068,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>553049</v>
+        <v>552824</v>
       </c>
       <c r="R33" t="n">
-        <v>6469673</v>
+        <v>6469659</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4110,17 +4106,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4132,14 +4124,14 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131344704</v>
+        <v>131344646</v>
       </c>
       <c r="B34" t="n">
         <v>99038</v>
@@ -4169,7 +4161,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -4182,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552824</v>
+        <v>552813</v>
       </c>
       <c r="R34" t="n">
-        <v>6469659</v>
+        <v>6469703</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4238,49 +4230,53 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Emil Ideskär</t>
+          <t>Emil Ideskär, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131344646</v>
+        <v>131344674</v>
       </c>
       <c r="B35" t="n">
-        <v>99038</v>
+        <v>57899</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4288,10 +4284,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552813</v>
+        <v>552930</v>
       </c>
       <c r="R35" t="n">
-        <v>6469703</v>
+        <v>6469714</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4326,13 +4322,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -792,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131344692</v>
+        <v>131344703</v>
       </c>
       <c r="B3" t="n">
-        <v>79883</v>
+        <v>99044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,6 +827,7 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552907</v>
+        <v>552843</v>
       </c>
       <c r="R3" t="n">
-        <v>6469684</v>
+        <v>6469679</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131344703</v>
+        <v>131344676</v>
       </c>
       <c r="B4" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,7 +928,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -940,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552843</v>
+        <v>552946</v>
       </c>
       <c r="R4" t="n">
-        <v>6469679</v>
+        <v>6469707</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131344676</v>
+        <v>131344688</v>
       </c>
       <c r="B5" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1046,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552946</v>
+        <v>552928</v>
       </c>
       <c r="R5" t="n">
-        <v>6469707</v>
+        <v>6469662</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131344688</v>
+        <v>131344684</v>
       </c>
       <c r="B6" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,7 +1140,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1152,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552928</v>
+        <v>552919</v>
       </c>
       <c r="R6" t="n">
-        <v>6469662</v>
+        <v>6469667</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,42 +1216,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131344684</v>
+        <v>131344692</v>
       </c>
       <c r="B7" t="n">
-        <v>99038</v>
+        <v>79885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552919</v>
+        <v>552907</v>
       </c>
       <c r="R7" t="n">
-        <v>6469667</v>
+        <v>6469684</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1324,7 @@
         <v>131344679</v>
       </c>
       <c r="B8" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>131344678</v>
       </c>
       <c r="B9" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>131344654</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>131344696</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>131344689</v>
       </c>
       <c r="B12" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>131344647</v>
       </c>
       <c r="B13" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>131344649</v>
       </c>
       <c r="B14" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,41 +2085,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344698</v>
+        <v>131344707</v>
       </c>
       <c r="B15" t="n">
-        <v>79883</v>
+        <v>101249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2127,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552887</v>
+        <v>552818</v>
       </c>
       <c r="R15" t="n">
-        <v>6469694</v>
+        <v>6469626</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,42 +2191,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344707</v>
+        <v>131344698</v>
       </c>
       <c r="B16" t="n">
-        <v>101243</v>
+        <v>79885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552818</v>
+        <v>552887</v>
       </c>
       <c r="R16" t="n">
-        <v>6469626</v>
+        <v>6469694</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,49 +2289,52 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Emil Ideskär</t>
+          <t>Emil Ideskär, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131344651</v>
+        <v>131344652</v>
       </c>
       <c r="B17" t="n">
-        <v>99038</v>
+        <v>91859</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2339,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552908</v>
+        <v>552916</v>
       </c>
       <c r="R17" t="n">
-        <v>6469775</v>
+        <v>6469751</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,42 +2405,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344677</v>
+        <v>131344686</v>
       </c>
       <c r="B18" t="n">
-        <v>106160</v>
+        <v>79885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2445,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552948</v>
+        <v>552925</v>
       </c>
       <c r="R18" t="n">
-        <v>6469713</v>
+        <v>6469645</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,42 +2510,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344668</v>
+        <v>131344682</v>
       </c>
       <c r="B19" t="n">
-        <v>99038</v>
+        <v>57901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2551,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552947</v>
+        <v>552956</v>
       </c>
       <c r="R19" t="n">
-        <v>6469715</v>
+        <v>6469666</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,13 +2595,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2614,41 +2624,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344686</v>
+        <v>131344677</v>
       </c>
       <c r="B20" t="n">
-        <v>79883</v>
+        <v>106166</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2656,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552925</v>
+        <v>552948</v>
       </c>
       <c r="R20" t="n">
-        <v>6469645</v>
+        <v>6469713</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2719,45 +2730,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344652</v>
+        <v>131344651</v>
       </c>
       <c r="B21" t="n">
-        <v>91853</v>
+        <v>99044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2765,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552916</v>
+        <v>552908</v>
       </c>
       <c r="R21" t="n">
-        <v>6469751</v>
+        <v>6469775</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,46 +2836,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131344682</v>
+        <v>131344668</v>
       </c>
       <c r="B22" t="n">
-        <v>57899</v>
+        <v>99044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2875,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552956</v>
+        <v>552947</v>
       </c>
       <c r="R22" t="n">
-        <v>6469666</v>
+        <v>6469715</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,17 +2917,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>131344683</v>
       </c>
       <c r="B23" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>131344687</v>
       </c>
       <c r="B24" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>131344648</v>
       </c>
       <c r="B25" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,45 +3260,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131344663</v>
+        <v>131344650</v>
       </c>
       <c r="B26" t="n">
-        <v>91853</v>
+        <v>99044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3306,10 +3303,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>553051</v>
+        <v>552899</v>
       </c>
       <c r="R26" t="n">
-        <v>6469833</v>
+        <v>6469774</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3369,10 +3366,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131344658</v>
+        <v>131344663</v>
       </c>
       <c r="B27" t="n">
-        <v>57899</v>
+        <v>91859</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3380,21 +3377,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3402,13 +3399,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3416,10 +3412,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>553131</v>
+        <v>553051</v>
       </c>
       <c r="R27" t="n">
-        <v>6469899</v>
+        <v>6469833</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3454,17 +3450,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3483,42 +3475,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131344650</v>
+        <v>131344658</v>
       </c>
       <c r="B28" t="n">
-        <v>99038</v>
+        <v>57901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3526,10 +3522,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>552899</v>
+        <v>553131</v>
       </c>
       <c r="R28" t="n">
-        <v>6469774</v>
+        <v>6469899</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3564,13 +3560,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>131344670</v>
       </c>
       <c r="B29" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>131344660</v>
       </c>
       <c r="B30" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>131344653</v>
       </c>
       <c r="B31" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3915,42 +3915,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131344666</v>
+        <v>131344704</v>
       </c>
       <c r="B32" t="n">
-        <v>57899</v>
+        <v>99044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>553049</v>
+        <v>552824</v>
       </c>
       <c r="R32" t="n">
-        <v>6469673</v>
+        <v>6469659</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,17 +3996,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4025,10 +4021,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131344704</v>
+        <v>131344646</v>
       </c>
       <c r="B33" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4055,7 +4051,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4068,10 +4064,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552824</v>
+        <v>552813</v>
       </c>
       <c r="R33" t="n">
-        <v>6469659</v>
+        <v>6469703</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4124,49 +4120,53 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Emil Ideskär</t>
+          <t>Emil Ideskär, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131344646</v>
+        <v>131344674</v>
       </c>
       <c r="B34" t="n">
-        <v>99038</v>
+        <v>57901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552813</v>
+        <v>552930</v>
       </c>
       <c r="R34" t="n">
-        <v>6469703</v>
+        <v>6469714</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4212,13 +4212,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4237,10 +4241,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131344674</v>
+        <v>131344666</v>
       </c>
       <c r="B35" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4265,11 +4269,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552930</v>
+        <v>553049</v>
       </c>
       <c r="R35" t="n">
-        <v>6469714</v>
+        <v>6469673</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4354,7 +4354,7 @@
         <v>131344680</v>
       </c>
       <c r="B36" t="n">
-        <v>101243</v>
+        <v>101249</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>131344691</v>
       </c>
       <c r="B37" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>131344661</v>
       </c>
       <c r="B38" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>131344659</v>
       </c>
       <c r="B39" t="n">
-        <v>97903</v>
+        <v>97909</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>131344705</v>
       </c>
       <c r="B40" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4880,52 +4880,49 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Emil Ideskär</t>
+          <t>Emil Ideskär, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131344662</v>
+        <v>131344645</v>
       </c>
       <c r="B41" t="n">
-        <v>91853</v>
+        <v>99044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4933,10 +4930,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>553053</v>
+        <v>552818</v>
       </c>
       <c r="R41" t="n">
-        <v>6469836</v>
+        <v>6469702</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4996,42 +4993,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131344645</v>
+        <v>131344662</v>
       </c>
       <c r="B42" t="n">
-        <v>99038</v>
+        <v>91859</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>552818</v>
+        <v>553053</v>
       </c>
       <c r="R42" t="n">
-        <v>6469702</v>
+        <v>6469836</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5105,7 +5105,7 @@
         <v>131344656</v>
       </c>
       <c r="B43" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5208,10 +5208,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131344706</v>
+        <v>131344673</v>
       </c>
       <c r="B44" t="n">
-        <v>57899</v>
+        <v>58061</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552813</v>
+        <v>552942</v>
       </c>
       <c r="R44" t="n">
-        <v>6469628</v>
+        <v>6469709</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5293,11 +5293,6 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5315,7 +5310,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Emil Ideskär</t>
+          <t>Emil Ideskär, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5325,7 +5320,7 @@
         <v>131344669</v>
       </c>
       <c r="B45" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5431,7 +5426,7 @@
         <v>131344685</v>
       </c>
       <c r="B46" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5537,7 +5532,7 @@
         <v>131344675</v>
       </c>
       <c r="B47" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5643,7 +5638,7 @@
         <v>131344667</v>
       </c>
       <c r="B48" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5749,7 +5744,7 @@
         <v>131344657</v>
       </c>
       <c r="B49" t="n">
-        <v>101243</v>
+        <v>101249</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5852,10 +5847,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131344673</v>
+        <v>131344706</v>
       </c>
       <c r="B50" t="n">
-        <v>58059</v>
+        <v>57901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5863,16 +5858,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5899,10 +5894,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552942</v>
+        <v>552813</v>
       </c>
       <c r="R50" t="n">
-        <v>6469709</v>
+        <v>6469628</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5935,6 +5930,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5964,7 +5964,7 @@
         <v>131344655</v>
       </c>
       <c r="B51" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -792,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131344703</v>
+        <v>131344692</v>
       </c>
       <c r="B3" t="n">
-        <v>99044</v>
+        <v>79885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,7 +827,6 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552843</v>
+        <v>552907</v>
       </c>
       <c r="R3" t="n">
-        <v>6469679</v>
+        <v>6469684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131344676</v>
+        <v>131344703</v>
       </c>
       <c r="B4" t="n">
         <v>99044</v>
@@ -928,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -941,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552946</v>
+        <v>552843</v>
       </c>
       <c r="R4" t="n">
-        <v>6469707</v>
+        <v>6469679</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +1003,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131344688</v>
+        <v>131344676</v>
       </c>
       <c r="B5" t="n">
         <v>99044</v>
@@ -1034,7 +1033,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1047,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552928</v>
+        <v>552946</v>
       </c>
       <c r="R5" t="n">
-        <v>6469662</v>
+        <v>6469707</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131344684</v>
+        <v>131344688</v>
       </c>
       <c r="B6" t="n">
         <v>99044</v>
@@ -1140,7 +1139,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1153,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552919</v>
+        <v>552928</v>
       </c>
       <c r="R6" t="n">
-        <v>6469667</v>
+        <v>6469662</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,41 +1215,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131344692</v>
+        <v>131344684</v>
       </c>
       <c r="B7" t="n">
-        <v>79885</v>
+        <v>99044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552907</v>
+        <v>552919</v>
       </c>
       <c r="R7" t="n">
-        <v>6469684</v>
+        <v>6469667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131344679</v>
+        <v>131344654</v>
       </c>
       <c r="B8" t="n">
-        <v>91859</v>
+        <v>57901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1354,12 +1354,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552958</v>
+        <v>552967</v>
       </c>
       <c r="R8" t="n">
-        <v>6469695</v>
+        <v>6469782</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,13 +1406,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1430,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131344678</v>
+        <v>131344679</v>
       </c>
       <c r="B9" t="n">
         <v>91859</v>
@@ -1460,7 +1465,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1476,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552948</v>
+        <v>552958</v>
       </c>
       <c r="R9" t="n">
-        <v>6469706</v>
+        <v>6469695</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131344654</v>
+        <v>131344678</v>
       </c>
       <c r="B10" t="n">
-        <v>57901</v>
+        <v>91859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,35 +1555,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1586,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552967</v>
+        <v>552948</v>
       </c>
       <c r="R10" t="n">
-        <v>6469782</v>
+        <v>6469706</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,17 +1628,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2296,45 +2296,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131344652</v>
+        <v>131344677</v>
       </c>
       <c r="B17" t="n">
-        <v>91859</v>
+        <v>106166</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2342,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552916</v>
+        <v>552948</v>
       </c>
       <c r="R17" t="n">
-        <v>6469751</v>
+        <v>6469713</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2405,41 +2402,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344686</v>
+        <v>131344651</v>
       </c>
       <c r="B18" t="n">
-        <v>79885</v>
+        <v>99044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2447,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552925</v>
+        <v>552908</v>
       </c>
       <c r="R18" t="n">
-        <v>6469645</v>
+        <v>6469775</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2510,46 +2508,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344682</v>
+        <v>131344668</v>
       </c>
       <c r="B19" t="n">
-        <v>57901</v>
+        <v>99044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2557,10 +2551,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552956</v>
+        <v>552947</v>
       </c>
       <c r="R19" t="n">
-        <v>6469666</v>
+        <v>6469715</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,17 +2589,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2624,42 +2614,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344677</v>
+        <v>131344652</v>
       </c>
       <c r="B20" t="n">
-        <v>106166</v>
+        <v>91859</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2667,10 +2660,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552948</v>
+        <v>552916</v>
       </c>
       <c r="R20" t="n">
-        <v>6469713</v>
+        <v>6469751</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,42 +2723,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344651</v>
+        <v>131344686</v>
       </c>
       <c r="B21" t="n">
-        <v>99044</v>
+        <v>79885</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2773,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552908</v>
+        <v>552925</v>
       </c>
       <c r="R21" t="n">
-        <v>6469775</v>
+        <v>6469645</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,42 +2828,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131344668</v>
+        <v>131344682</v>
       </c>
       <c r="B22" t="n">
-        <v>99044</v>
+        <v>57901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2879,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552947</v>
+        <v>552956</v>
       </c>
       <c r="R22" t="n">
-        <v>6469715</v>
+        <v>6469666</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2917,13 +2913,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3915,42 +3915,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131344704</v>
+        <v>131344674</v>
       </c>
       <c r="B32" t="n">
-        <v>99044</v>
+        <v>57901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3958,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552824</v>
+        <v>552930</v>
       </c>
       <c r="R32" t="n">
-        <v>6469659</v>
+        <v>6469714</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,13 +4000,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4021,42 +4029,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131344646</v>
+        <v>131344666</v>
       </c>
       <c r="B33" t="n">
-        <v>99044</v>
+        <v>57901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4064,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552813</v>
+        <v>553049</v>
       </c>
       <c r="R33" t="n">
-        <v>6469703</v>
+        <v>6469673</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4102,13 +4110,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4127,46 +4139,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131344674</v>
+        <v>131344704</v>
       </c>
       <c r="B34" t="n">
-        <v>57901</v>
+        <v>99044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4174,10 +4182,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552930</v>
+        <v>552824</v>
       </c>
       <c r="R34" t="n">
-        <v>6469714</v>
+        <v>6469659</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4212,17 +4220,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4241,42 +4245,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131344666</v>
+        <v>131344646</v>
       </c>
       <c r="B35" t="n">
-        <v>57901</v>
+        <v>99044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4284,10 +4288,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>553049</v>
+        <v>552813</v>
       </c>
       <c r="R35" t="n">
-        <v>6469673</v>
+        <v>6469703</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4322,17 +4326,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4563,56 +4563,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131344661</v>
+        <v>131344659</v>
       </c>
       <c r="B38" t="n">
-        <v>91859</v>
+        <v>97909</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>553051</v>
+        <v>553082</v>
       </c>
       <c r="R38" t="n">
-        <v>6469846</v>
+        <v>6469843</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4653,7 +4646,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4672,49 +4664,56 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131344659</v>
+        <v>131344661</v>
       </c>
       <c r="B39" t="n">
-        <v>97909</v>
+        <v>91859</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>553082</v>
+        <v>553051</v>
       </c>
       <c r="R39" t="n">
-        <v>6469843</v>
+        <v>6469846</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4755,6 +4754,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -1767,42 +1767,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131344689</v>
+        <v>131344698</v>
       </c>
       <c r="B12" t="n">
-        <v>99044</v>
+        <v>79885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1810,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552921</v>
+        <v>552887</v>
       </c>
       <c r="R12" t="n">
-        <v>6469663</v>
+        <v>6469694</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,7 +1872,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344647</v>
+        <v>131344689</v>
       </c>
       <c r="B13" t="n">
         <v>99044</v>
@@ -1903,7 +1902,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1916,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552884</v>
+        <v>552921</v>
       </c>
       <c r="R13" t="n">
-        <v>6469766</v>
+        <v>6469663</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,7 +1978,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344649</v>
+        <v>131344647</v>
       </c>
       <c r="B14" t="n">
         <v>99044</v>
@@ -2009,7 +2008,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2022,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552893</v>
+        <v>552884</v>
       </c>
       <c r="R14" t="n">
-        <v>6469762</v>
+        <v>6469766</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,37 +2084,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344707</v>
+        <v>131344649</v>
       </c>
       <c r="B15" t="n">
-        <v>101249</v>
+        <v>99044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2128,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552818</v>
+        <v>552893</v>
       </c>
       <c r="R15" t="n">
-        <v>6469626</v>
+        <v>6469762</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,41 +2190,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344698</v>
+        <v>131344707</v>
       </c>
       <c r="B16" t="n">
-        <v>79885</v>
+        <v>101249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552887</v>
+        <v>552818</v>
       </c>
       <c r="R16" t="n">
-        <v>6469694</v>
+        <v>6469626</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,42 +2296,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131344677</v>
+        <v>131344652</v>
       </c>
       <c r="B17" t="n">
-        <v>106166</v>
+        <v>91859</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2339,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552948</v>
+        <v>552916</v>
       </c>
       <c r="R17" t="n">
-        <v>6469713</v>
+        <v>6469751</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,42 +2405,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344651</v>
+        <v>131344686</v>
       </c>
       <c r="B18" t="n">
-        <v>99044</v>
+        <v>79885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2445,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552908</v>
+        <v>552925</v>
       </c>
       <c r="R18" t="n">
-        <v>6469775</v>
+        <v>6469645</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,37 +2510,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344668</v>
+        <v>131344677</v>
       </c>
       <c r="B19" t="n">
-        <v>99044</v>
+        <v>106166</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2551,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552947</v>
+        <v>552948</v>
       </c>
       <c r="R19" t="n">
-        <v>6469715</v>
+        <v>6469713</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,45 +2616,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344652</v>
+        <v>131344651</v>
       </c>
       <c r="B20" t="n">
-        <v>91859</v>
+        <v>99044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2660,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552916</v>
+        <v>552908</v>
       </c>
       <c r="R20" t="n">
-        <v>6469751</v>
+        <v>6469775</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2723,41 +2722,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344686</v>
+        <v>131344668</v>
       </c>
       <c r="B21" t="n">
-        <v>79885</v>
+        <v>99044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552925</v>
+        <v>552947</v>
       </c>
       <c r="R21" t="n">
-        <v>6469645</v>
+        <v>6469715</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3915,46 +3915,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131344674</v>
+        <v>131344704</v>
       </c>
       <c r="B32" t="n">
-        <v>57901</v>
+        <v>99044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3962,10 +3958,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552930</v>
+        <v>552824</v>
       </c>
       <c r="R32" t="n">
-        <v>6469714</v>
+        <v>6469659</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4000,17 +3996,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4029,42 +4021,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131344666</v>
+        <v>131344646</v>
       </c>
       <c r="B33" t="n">
-        <v>57901</v>
+        <v>99044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4072,10 +4064,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>553049</v>
+        <v>552813</v>
       </c>
       <c r="R33" t="n">
-        <v>6469673</v>
+        <v>6469703</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4110,17 +4102,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4139,42 +4127,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131344704</v>
+        <v>131344674</v>
       </c>
       <c r="B34" t="n">
-        <v>99044</v>
+        <v>57901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4182,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552824</v>
+        <v>552930</v>
       </c>
       <c r="R34" t="n">
-        <v>6469659</v>
+        <v>6469714</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4220,13 +4212,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4245,42 +4241,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131344646</v>
+        <v>131344666</v>
       </c>
       <c r="B35" t="n">
-        <v>99044</v>
+        <v>57901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4288,10 +4284,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552813</v>
+        <v>553049</v>
       </c>
       <c r="R35" t="n">
-        <v>6469703</v>
+        <v>6469673</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4326,13 +4322,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4563,49 +4563,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131344659</v>
+        <v>131344661</v>
       </c>
       <c r="B38" t="n">
-        <v>97909</v>
+        <v>91859</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>553082</v>
+        <v>553051</v>
       </c>
       <c r="R38" t="n">
-        <v>6469843</v>
+        <v>6469846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4646,6 +4653,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4664,56 +4672,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131344661</v>
+        <v>131344659</v>
       </c>
       <c r="B39" t="n">
-        <v>91859</v>
+        <v>97909</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>553051</v>
+        <v>553082</v>
       </c>
       <c r="R39" t="n">
-        <v>6469846</v>
+        <v>6469843</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4754,7 +4755,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -792,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131344692</v>
+        <v>131344703</v>
       </c>
       <c r="B3" t="n">
-        <v>79885</v>
+        <v>99044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,6 +827,7 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552907</v>
+        <v>552843</v>
       </c>
       <c r="R3" t="n">
-        <v>6469684</v>
+        <v>6469679</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131344703</v>
+        <v>131344676</v>
       </c>
       <c r="B4" t="n">
         <v>99044</v>
@@ -927,7 +928,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -940,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552843</v>
+        <v>552946</v>
       </c>
       <c r="R4" t="n">
-        <v>6469679</v>
+        <v>6469707</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1004,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131344676</v>
+        <v>131344688</v>
       </c>
       <c r="B5" t="n">
         <v>99044</v>
@@ -1033,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1046,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552946</v>
+        <v>552928</v>
       </c>
       <c r="R5" t="n">
-        <v>6469707</v>
+        <v>6469662</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131344688</v>
+        <v>131344684</v>
       </c>
       <c r="B6" t="n">
         <v>99044</v>
@@ -1139,7 +1140,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1152,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552928</v>
+        <v>552919</v>
       </c>
       <c r="R6" t="n">
-        <v>6469662</v>
+        <v>6469667</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,42 +1216,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131344684</v>
+        <v>131344692</v>
       </c>
       <c r="B7" t="n">
-        <v>99044</v>
+        <v>79885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552919</v>
+        <v>552907</v>
       </c>
       <c r="R7" t="n">
-        <v>6469667</v>
+        <v>6469684</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2296,45 +2296,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131344652</v>
+        <v>131344677</v>
       </c>
       <c r="B17" t="n">
-        <v>91859</v>
+        <v>106166</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2342,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552916</v>
+        <v>552948</v>
       </c>
       <c r="R17" t="n">
-        <v>6469751</v>
+        <v>6469713</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2405,41 +2402,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131344686</v>
+        <v>131344651</v>
       </c>
       <c r="B18" t="n">
-        <v>79885</v>
+        <v>99044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2447,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552925</v>
+        <v>552908</v>
       </c>
       <c r="R18" t="n">
-        <v>6469645</v>
+        <v>6469775</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2510,37 +2508,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131344677</v>
+        <v>131344668</v>
       </c>
       <c r="B19" t="n">
-        <v>106166</v>
+        <v>99044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2553,10 +2551,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552948</v>
+        <v>552947</v>
       </c>
       <c r="R19" t="n">
-        <v>6469713</v>
+        <v>6469715</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2616,42 +2614,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131344651</v>
+        <v>131344652</v>
       </c>
       <c r="B20" t="n">
-        <v>99044</v>
+        <v>91859</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2659,10 +2660,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552908</v>
+        <v>552916</v>
       </c>
       <c r="R20" t="n">
-        <v>6469775</v>
+        <v>6469751</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,42 +2723,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131344668</v>
+        <v>131344686</v>
       </c>
       <c r="B21" t="n">
-        <v>99044</v>
+        <v>79885</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552947</v>
+        <v>552925</v>
       </c>
       <c r="R21" t="n">
-        <v>6469715</v>
+        <v>6469645</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -4563,56 +4563,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131344661</v>
+        <v>131344659</v>
       </c>
       <c r="B38" t="n">
-        <v>91859</v>
+        <v>97909</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>553051</v>
+        <v>553082</v>
       </c>
       <c r="R38" t="n">
-        <v>6469846</v>
+        <v>6469843</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4653,7 +4646,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4672,49 +4664,56 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131344659</v>
+        <v>131344661</v>
       </c>
       <c r="B39" t="n">
-        <v>97909</v>
+        <v>91859</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>553082</v>
+        <v>553051</v>
       </c>
       <c r="R39" t="n">
-        <v>6469843</v>
+        <v>6469846</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4755,6 +4754,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7186-2026 artfynd.xlsx
+++ b/artfynd/A 7186-2026 artfynd.xlsx
@@ -792,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131344703</v>
+        <v>131344692</v>
       </c>
       <c r="B3" t="n">
-        <v>99044</v>
+        <v>79885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,7 +827,6 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552843</v>
+        <v>552907</v>
       </c>
       <c r="R3" t="n">
-        <v>6469679</v>
+        <v>6469684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131344676</v>
+        <v>131344703</v>
       </c>
       <c r="B4" t="n">
         <v>99044</v>
@@ -928,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -941,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552946</v>
+        <v>552843</v>
       </c>
       <c r="R4" t="n">
-        <v>6469707</v>
+        <v>6469679</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +1003,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131344688</v>
+        <v>131344676</v>
       </c>
       <c r="B5" t="n">
         <v>99044</v>
@@ -1034,7 +1033,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1047,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552928</v>
+        <v>552946</v>
       </c>
       <c r="R5" t="n">
-        <v>6469662</v>
+        <v>6469707</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131344684</v>
+        <v>131344688</v>
       </c>
       <c r="B6" t="n">
         <v>99044</v>
@@ -1140,7 +1139,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1153,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552919</v>
+        <v>552928</v>
       </c>
       <c r="R6" t="n">
-        <v>6469667</v>
+        <v>6469662</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,41 +1215,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131344692</v>
+        <v>131344684</v>
       </c>
       <c r="B7" t="n">
-        <v>79885</v>
+        <v>99044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552907</v>
+        <v>552919</v>
       </c>
       <c r="R7" t="n">
-        <v>6469684</v>
+        <v>6469667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131344654</v>
+        <v>131344679</v>
       </c>
       <c r="B8" t="n">
-        <v>57901</v>
+        <v>91859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1354,13 +1354,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552967</v>
+        <v>552958</v>
       </c>
       <c r="R8" t="n">
-        <v>6469782</v>
+        <v>6469695</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,17 +1405,13 @@
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1435,7 +1430,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131344679</v>
+        <v>131344678</v>
       </c>
       <c r="B9" t="n">
         <v>91859</v>
@@ -1465,7 +1460,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1481,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552958</v>
+        <v>552948</v>
       </c>
       <c r="R9" t="n">
-        <v>6469695</v>
+        <v>6469706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131344678</v>
+        <v>131344654</v>
       </c>
       <c r="B10" t="n">
-        <v>91859</v>
+        <v>57901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,34 +1550,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1590,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552948</v>
+        <v>552967</v>
       </c>
       <c r="R10" t="n">
-        <v>6469706</v>
+        <v>6469782</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,13 +1624,17 @@
           <t>2026-02-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1767,41 +1767,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131344698</v>
+        <v>131344689</v>
       </c>
       <c r="B12" t="n">
-        <v>79885</v>
+        <v>99044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1809,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552887</v>
+        <v>552921</v>
       </c>
       <c r="R12" t="n">
-        <v>6469694</v>
+        <v>6469663</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,7 +1873,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131344689</v>
+        <v>131344647</v>
       </c>
       <c r="B13" t="n">
         <v>99044</v>
@@ -1902,7 +1903,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1915,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552921</v>
+        <v>552884</v>
       </c>
       <c r="R13" t="n">
-        <v>6469663</v>
+        <v>6469766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,7 +1979,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131344647</v>
+        <v>131344649</v>
       </c>
       <c r="B14" t="n">
         <v>99044</v>
@@ -2008,7 +2009,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2021,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552884</v>
+        <v>552893</v>
       </c>
       <c r="R14" t="n">
-        <v>6469766</v>
+        <v>6469762</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,37 +2085,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131344649</v>
+        <v>131344707</v>
       </c>
       <c r="B15" t="n">
-        <v>99044</v>
+        <v>101249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2127,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552893</v>
+        <v>552818</v>
       </c>
       <c r="R15" t="n">
-        <v>6469762</v>
+        <v>6469626</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,42 +2191,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131344707</v>
+        <v>131344698</v>
       </c>
       <c r="B16" t="n">
-        <v>101249</v>
+        <v>79885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552818</v>
+        <v>552887</v>
       </c>
       <c r="R16" t="n">
-        <v>6469626</v>
+        <v>6469694</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -4563,49 +4563,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131344659</v>
+        <v>131344661</v>
       </c>
       <c r="B38" t="n">
-        <v>97909</v>
+        <v>91859</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>553082</v>
+        <v>553051</v>
       </c>
       <c r="R38" t="n">
-        <v>6469843</v>
+        <v>6469846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4646,6 +4653,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4664,56 +4672,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131344661</v>
+        <v>131344659</v>
       </c>
       <c r="B39" t="n">
-        <v>91859</v>
+        <v>97909</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Ändlöten, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>553051</v>
+        <v>553082</v>
       </c>
       <c r="R39" t="n">
-        <v>6469846</v>
+        <v>6469843</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4754,7 +4755,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4887,42 +4887,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131344645</v>
+        <v>131344662</v>
       </c>
       <c r="B41" t="n">
-        <v>99044</v>
+        <v>91859</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4930,10 +4933,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>552818</v>
+        <v>553053</v>
       </c>
       <c r="R41" t="n">
-        <v>6469702</v>
+        <v>6469836</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4993,45 +4996,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131344662</v>
+        <v>131344645</v>
       </c>
       <c r="B42" t="n">
-        <v>91859</v>
+        <v>99044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>553053</v>
+        <v>552818</v>
       </c>
       <c r="R42" t="n">
-        <v>6469836</v>
+        <v>6469702</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
